--- a/files/九龙-何文田-傲玟.xlsx
+++ b/files/九龙-何文田-傲玟.xlsx
@@ -11814,27 +11814,23 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H242" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I242" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="H242" s="5" t="n">
+        <v>20648000</v>
+      </c>
+      <c r="I242" s="5" t="n">
+        <v>23200</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19557,10 +19553,34 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>27/F</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>B | 1442呎 (1房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>27&amp;28&amp;29/F</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>A | 6681呎 (4+房)
 暂无价格
@@ -19568,32 +19588,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1442呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
+      <c r="C8" s="16" t="inlineStr"/>
+      <c r="D8" s="16" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -22213,7 +22209,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>1 套</t>
+          <t>0 套</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -22223,7 +22219,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>19 套</t>
+          <t>20 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -22407,12 +22403,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
-招标单位
--
-(在售)</t>
+$2,065万
+$23,200/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
@@ -23036,11 +23032,36 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>20/F</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr"/>
+      <c r="C7" s="16" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1,924万
+$23,811/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1,934万
+$23,931/呎
+(已售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>20&amp;21/F</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr"/>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>B | 2905呎 (4+房)
 $9,870万
@@ -23048,42 +23069,35 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1,924万
-$23,811/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1,934万
-$23,931/呎
-(已售)</t>
-        </is>
-      </c>
+      <c r="D8" s="16" t="inlineStr"/>
+      <c r="E8" s="16" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>19&amp;20/F</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>A | 2258呎 (4+房)
+$7,128万
+$31,568/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr"/>
+      <c r="D9" s="16" t="inlineStr"/>
+      <c r="E9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10" ht="65" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>19/F</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr"/>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr"/>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>B | 1264呎 (3房)
 $3,021万
@@ -23091,7 +23105,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1,912万
@@ -23099,7 +23113,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1,916万
@@ -23107,24 +23121,6 @@
 (已售)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19&amp;20/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 2258呎 (4+房)
-$7,128万
-$31,568/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
     </row>
     <row r="11" ht="65" customHeight="1">
       <c r="A11" s="2" t="inlineStr">

--- a/files/九龙-何文田-傲玟.xlsx
+++ b/files/九龙-何文田-傲玟.xlsx
@@ -8,12 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座 销控表" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座 销控表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -116,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -181,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -197,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -909,7 +765,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -955,7 +811,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1001,7 +857,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1047,7 +903,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1093,7 +949,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1189,7 +1045,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1235,7 +1091,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1331,7 +1187,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1377,7 +1233,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1473,7 +1329,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1519,7 +1375,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1615,7 +1471,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1661,7 +1517,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1757,7 +1613,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1803,7 +1659,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1849,7 +1705,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1895,7 +1751,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1941,7 +1797,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1987,7 +1843,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2033,7 +1889,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2079,7 +1935,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2125,7 +1981,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2171,7 +2027,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2217,7 +2073,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2313,7 +2169,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2359,7 +2215,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2405,7 +2261,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2451,7 +2307,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2497,7 +2353,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2589,7 +2445,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2635,7 +2491,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2731,7 +2587,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2777,7 +2633,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2873,7 +2729,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2919,7 +2775,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3015,7 +2871,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3061,7 +2917,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3157,7 +3013,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3203,7 +3059,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3299,7 +3155,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3345,7 +3201,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3391,7 +3247,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3437,7 +3293,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3483,7 +3339,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3529,7 +3385,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3575,7 +3431,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3621,7 +3477,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3667,7 +3523,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3713,7 +3569,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3759,7 +3615,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3855,7 +3711,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3901,7 +3757,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3947,7 +3803,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3993,7 +3849,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4039,7 +3895,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4085,7 +3941,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4131,7 +3987,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4177,7 +4033,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4223,7 +4079,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4269,7 +4125,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4315,7 +4171,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4361,7 +4217,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4407,7 +4263,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4453,7 +4309,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4499,7 +4355,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4545,7 +4401,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4591,7 +4447,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4637,7 +4493,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4729,7 +4585,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4775,7 +4631,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4812,7 +4668,7 @@
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>1244</v>
+        <v>1180</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
@@ -4821,14 +4677,14 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
         <v>30843600</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>24794</v>
+        <v>26139</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -4867,7 +4723,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4913,7 +4769,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4959,7 +4815,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -5005,7 +4861,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5051,7 +4907,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5097,7 +4953,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5143,7 +4999,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5189,7 +5045,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5235,7 +5091,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5281,7 +5137,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5327,7 +5183,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5373,7 +5229,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5419,7 +5275,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5465,7 +5321,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5511,7 +5367,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5557,7 +5413,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5603,7 +5459,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5649,7 +5505,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5745,7 +5601,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5791,7 +5647,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5837,7 +5693,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5883,7 +5739,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5929,7 +5785,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5975,7 +5831,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-27</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6021,7 +5877,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6067,7 +5923,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6113,7 +5969,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6159,7 +6015,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6205,7 +6061,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6251,7 +6107,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-14</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6297,7 +6153,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-12-11</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6343,7 +6199,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6389,7 +6245,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-14</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6435,7 +6291,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-25</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6481,7 +6337,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6527,7 +6383,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6573,7 +6429,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6619,7 +6475,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6665,7 +6521,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-27</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6711,7 +6567,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-19</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6757,7 +6613,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6803,7 +6659,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6849,7 +6705,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6895,7 +6751,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6941,7 +6797,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6987,7 +6843,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7033,7 +6889,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7079,7 +6935,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7125,7 +6981,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7171,7 +7027,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7217,7 +7073,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7263,7 +7119,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7309,7 +7165,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7355,7 +7211,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7401,7 +7257,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7447,7 +7303,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7493,7 +7349,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7539,7 +7395,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7585,7 +7441,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7631,7 +7487,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7677,7 +7533,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7723,7 +7579,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7769,7 +7625,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7815,7 +7671,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7861,7 +7717,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7907,7 +7763,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7953,7 +7809,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7999,7 +7855,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8045,7 +7901,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8091,7 +7947,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8137,7 +7993,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8183,7 +8039,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8229,7 +8085,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8275,7 +8131,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8321,7 +8177,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8367,7 +8223,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8413,7 +8269,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8459,7 +8315,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8505,7 +8361,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8551,7 +8407,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8597,7 +8453,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8643,7 +8499,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8689,7 +8545,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8735,7 +8591,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -8781,7 +8637,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8827,7 +8683,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8873,7 +8729,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8919,7 +8775,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -8965,7 +8821,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -9011,7 +8867,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9057,7 +8913,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9103,7 +8959,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9149,7 +9005,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9195,7 +9051,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9241,7 +9097,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9287,7 +9143,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -9333,7 +9189,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9379,7 +9235,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9425,7 +9281,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9471,7 +9327,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9517,7 +9373,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9563,7 +9419,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9609,7 +9465,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9655,7 +9511,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9701,7 +9557,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -9747,7 +9603,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -9793,7 +9649,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -9839,7 +9695,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9885,7 +9741,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9931,7 +9787,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -9977,7 +9833,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -10023,7 +9879,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -10069,7 +9925,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10115,7 +9971,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-19</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10161,7 +10017,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-31</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10207,7 +10063,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10253,7 +10109,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10299,7 +10155,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10345,7 +10201,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10391,7 +10247,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10437,7 +10293,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10483,7 +10339,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10529,7 +10385,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10575,7 +10431,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -10621,7 +10477,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10667,7 +10523,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -10713,7 +10569,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10759,7 +10615,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -10805,7 +10661,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -10851,7 +10707,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -10897,7 +10753,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -10943,7 +10799,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -10989,7 +10845,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -11035,7 +10891,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11081,7 +10937,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11127,7 +10983,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11173,7 +11029,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -12207,7 +12063,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -12399,7 +12255,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -12545,7 +12401,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12591,7 +12447,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -12737,7 +12593,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -12783,7 +12639,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -12929,7 +12785,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -12975,7 +12831,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -13121,7 +12977,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -13167,7 +13023,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -13313,7 +13169,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -13359,7 +13215,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -13551,7 +13407,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -14289,7 +14145,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14335,7 +14191,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -14381,7 +14237,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -14427,7 +14283,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14473,7 +14329,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -14519,7 +14375,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -14565,7 +14421,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -14611,7 +14467,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -14657,7 +14513,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -14703,7 +14559,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14749,7 +14605,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -14795,7 +14651,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -14841,7 +14697,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -14887,7 +14743,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -14933,7 +14789,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -14979,7 +14835,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -15025,7 +14881,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -15071,7 +14927,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -15117,7 +14973,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -15163,7 +15019,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -15209,7 +15065,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -15255,7 +15111,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -15301,7 +15157,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -15347,7 +15203,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -15393,7 +15249,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -15439,7 +15295,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -15485,7 +15341,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -15531,7 +15387,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -15577,7 +15433,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -15623,7 +15479,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -15669,7 +15525,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -15715,7 +15571,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -15761,7 +15617,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -15807,7 +15663,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -15853,7 +15709,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -15899,7 +15755,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -15945,7 +15801,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -15991,7 +15847,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -16037,7 +15893,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -16083,7 +15939,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -16129,7 +15985,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -16175,7 +16031,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -16221,7 +16077,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -16267,7 +16123,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -16313,7 +16169,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -16359,7 +16215,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -16405,7 +16261,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -16451,7 +16307,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -16497,7 +16353,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -16543,7 +16399,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -16589,7 +16445,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-03</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -16635,7 +16491,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -16681,7 +16537,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-03</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -16727,7 +16583,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -16773,7 +16629,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -16819,7 +16675,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -16865,7 +16721,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -16911,7 +16767,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -16957,7 +16813,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -17003,7 +16859,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -17049,7 +16905,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -17095,7 +16951,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -17141,7 +16997,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -17187,7 +17043,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -17283,7 +17139,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -17329,7 +17185,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -17375,7 +17231,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -17421,7 +17277,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -17467,7 +17323,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -17513,7 +17369,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -17559,7 +17415,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -17605,7 +17461,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -17651,7 +17507,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -17697,7 +17553,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -17743,7 +17599,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -17889,7 +17745,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -17935,7 +17791,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -17981,7 +17837,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -18027,7 +17883,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -18123,7 +17979,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -18169,7 +18025,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -18265,7 +18121,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -18311,7 +18167,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -18407,7 +18263,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -18453,7 +18309,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -18499,7 +18355,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -18545,7 +18401,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -18591,7 +18447,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -18737,7 +18593,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -18783,7 +18639,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -18829,7 +18685,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -18875,7 +18731,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -18971,7 +18827,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -19017,7 +18873,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -19113,7 +18969,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -19159,7 +19015,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -19255,7 +19111,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -19301,7 +19157,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -19423,4872 +19279,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>傲玟 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>68 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>53 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28&amp;29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 2357呎 (4+房)
-$7,787万
-$33,037/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1442呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27&amp;28&amp;29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 6681呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 2669呎 (4+房)
-$7,877万
-$29,514/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$3,125万
-$26,347/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,612万
-$26,426/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,618万
-$26,444/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$3,002万
-$25,315/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,500万
-$25,604/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,473万
-$25,386/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,454万
-$25,264/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,429万
-$25,069/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,432万
-$25,105/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,742万
-$27,350/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,425万
-$25,052/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,734万
-$27,297/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,417万
-$24,999/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,727万
-$27,244/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,417万
-$24,999/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,340万
-$24,415/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2,753万
-$23,210/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,396万
-$24,841/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,321万
-$24,275/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2,852万
-$24,050/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,403万
-$24,894/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,313万
-$24,218/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2,830万
-$23,860/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$4,198万
-$30,710/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,270万
-$23,905/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,374万
-$24,682/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,227万
-$23,588/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2,792万
-$23,543/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,665万
-$26,811/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,270万
-$23,905/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-$2,815万
-$22,500/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,338万
-$24,418/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,205万
-$23,429/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,330万
-$24,360/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,212万
-$23,482/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,352万
-$24,524/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,209万
-$23,461/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,324万
-$24,312/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,193万
-$23,342/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,604万
-$26,364/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,180万
-$23,246/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,652万
-$26,719/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,154万
-$23,059/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2,555万
-$21,539/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 1445呎 (3房)
-$4,494万
-$31,100/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3,133万
-$22,901/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2,540万
-$21,413/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3,100万
-$22,677/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 1352呎 (3房)
-$3,032万
-$22,423/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2,527万
-$21,307/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;1/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 2626呎 (4+房)
-$6,828万
-$26,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr"/>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 2268呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>傲玟 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>69 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>68 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28&amp;29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 3461呎 (4+房)
-$12,067万
-$34,864/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 2334呎 (4+房)
-$7,700万
-$32,991/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27&amp;28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 2338呎 (4+房)
-$7,600万
-$32,506/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3,630万
-$26,866/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,612万
-$22,139/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 1325呎 (3房)
-$3,493万
-$26,366/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 1347呎 (3房)
-$3,548万
-$26,342/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,662万
-$22,561/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 1325呎 (3房)
-$3,479万
-$26,260/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1347呎 (3房)
-$3,491万
-$25,919/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,700万
-$22,881/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$3,115万
-$22,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$3,164万
-$22,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,612万
-$22,139/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 1325呎 (3房)
-$3,227万
-$24,354/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 1347呎 (3房)
-$3,349万
-$24,861/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,995万
-$25,380/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$3,073万
-$21,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$3,121万
-$21,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,749万
-$23,299/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$3,087万
-$22,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 1347呎 (3房)
-$3,206万
-$23,803/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 1244呎 (3房)
-$3,084万
-$24,794/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$3,146万
-$22,420/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$3,120万
-$21,896/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,608万
-$22,099/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$3,199万
-$22,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 1347呎 (3房)
-$3,164万
-$23,486/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,692万
-$22,814/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 1325呎 (3房)
-$3,115万
-$23,507/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 1347呎 (3房)
-$3,164万
-$23,486/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,580万
-$21,864/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$3,016万
-$21,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$2,878万
-$20,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,532万
-$21,454/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$4,378万
-$31,206/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$2,861万
-$20,080/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,488万
-$21,085/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$2,921万
-$20,820/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 1347呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 1244呎 (3房)
-$2,513万
-$20,200/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 1325呎 (3房)
-$2,908万
-$21,947/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$2,850万
-$20,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,415万
-$20,464/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 1325呎 (3房)
-$2,868万
-$21,642/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$4,225万
-$29,650/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,427万
-$20,570/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 1325呎 (3房)
-$2,778万
-$20,966/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 1347呎 (3房)
-$4,185万
-$31,066/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,140万
-$18,133/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$4,349万
-$31,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$4,175万
-$29,295/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,140万
-$18,133/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$4,021万
-$28,659/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$4,118万
-$28,902/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,132万
-$18,070/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 1325呎 (3房)
-$3,934万
-$29,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 1347呎 (3房)
-$4,086万
-$30,332/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,131万
-$18,059/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$3,931万
-$28,018/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$4,053万
-$28,445/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,130万
-$18,049/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$3,931万
-$28,018/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$4,041万
-$28,360/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,128万
-$18,038/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 1325呎 (3房)
-$2,804万
-$21,163/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 1330呎 (3房)
-$2,800万
-$21,053/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2,127万
-$18,027/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;1/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr"/>
-      <c r="C30" s="16" t="inlineStr"/>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 2251呎 (4+房)
-$5,853万
-$26,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>傲玟 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>90 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>90 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 1683呎 (4+房)
-$5,471万
-$32,505/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28&amp;29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11,039万
-$33,915/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,984万
-$23,479/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1,873万
-$22,169/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 2065呎 (4+房)
-$6,250万
-$30,266/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,978万
-$23,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1,883万
-$22,280/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 2002呎 (4+房)
-$6,254万
-$31,239/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,957万
-$23,157/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1,861万
-$22,025/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,677万
-$23,945/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,616万
-$22,689/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,915万
-$22,659/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,840万
-$21,806/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,650万
-$23,703/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,579万
-$22,368/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,943万
-$22,991/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,822万
-$21,584/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,610万
-$23,345/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,558万
-$22,183/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,868万
-$22,107/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,803万
-$21,361/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,892万
-$25,867/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,535万
-$21,987/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,840万
-$21,775/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,784万
-$21,139/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,560万
-$22,898/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,535万
-$21,987/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,905万
-$22,549/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,765万
-$20,916/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,542万
-$22,737/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,870万
-$24,892/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,882万
-$22,272/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,728万
-$20,471/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,535万
-$22,674/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,497万
-$21,660/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,873万
-$22,162/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,765万
-$20,916/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,505万
-$22,407/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,491万
-$21,606/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,857万
-$21,974/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,708万
-$20,237/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,493万
-$22,297/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,465万
-$21,379/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,840万
-$21,775/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,694万
-$20,071/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,473万
-$22,122/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,450万
-$21,249/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,831万
-$21,664/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,690万
-$20,026/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,456万
-$21,968/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,426万
-$21,040/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,812万
-$21,443/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,662万
-$19,692/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 1228呎 (3房)
-$3,616万
-$29,450/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,428万
-$21,062/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,804万
-$21,344/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,657万
-$19,637/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,438万
-$21,803/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,428万
-$21,062/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,800万
-$21,302/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,653万
-$19,581/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,419万
-$21,638/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,397万
-$20,789/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 934呎 (2房)
-$2,852万
-$30,538/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,648万
-$19,525/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 1228呎 (3房)
-$3,513万
-$28,610/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,384万
-$20,676/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$2,824万
-$33,422/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 939呎 (2房)
-$2,644万
-$28,160/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,395万
-$21,419/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,359万
-$20,460/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,775万
-$21,001/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,624万
-$19,247/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,368万
-$21,177/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,297万
-$19,919/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,765万
-$20,891/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,620万
-$19,192/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,364万
-$21,144/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,297万
-$19,919/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,763万
-$20,869/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,619万
-$19,181/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,337万
-$20,902/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,290万
-$19,864/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1,756万
-$20,780/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,619万
-$19,181/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 1118呎 (3房)
-$2,313万
-$20,691/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$2,284万
-$19,810/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 829呎 (2房)
-$1,726万
-$20,818/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 844呎 (2房)
-$1,618万
-$19,169/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>傲玟 - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>63 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>20 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>43 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>20&amp;21/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 3100呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 1747呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 1691呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>19&amp;20/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 898呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 892呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
-$2,065万
-$23,200/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 892呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
-$2,031万
-$22,820/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 892呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$2,011万
-$24,740/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 892呎 (2房)
-$1,962万
-$22,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$2,003万
-$24,637/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 892呎 (2房)
-$1,953万
-$21,900/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1,878万
-$23,098/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1,838万
-$22,630/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1,863万
-$22,912/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1,829万
-$22,520/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1,927万
-$23,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1,882万
-$23,177/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1,829万
-$22,496/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1,797万
-$22,135/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1,816万
-$22,332/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1,793万
-$22,080/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1,798万
-$22,113/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 892呎 (2房)
-$1,869万
-$20,950/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
-$1,860万
-$20,900/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1,860万
-$22,904/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 892呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 892呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>傲玟 - 6座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>64 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>64 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 1595呎 (4+房)
-$4,779万
-$29,964/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1,924万
-$23,811/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1,934万
-$23,931/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>20&amp;21/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 2905呎 (4+房)
-$9,870万
-$33,976/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>19&amp;20/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 2258呎 (4+房)
-$7,128万
-$31,568/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr"/>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$3,021万
-$23,902/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1,912万
-$23,663/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1,916万
-$23,712/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 1266呎 (3房)
-$3,067万
-$24,230/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$3,043万
-$24,074/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1,883万
-$23,308/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1,903万
-$23,547/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 1266呎 (3房)
-$2,983万
-$23,562/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$2,891万
-$22,873/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 878呎 (2房)
-$1,844万
-$21,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 887呎 (2房)
-$1,836万
-$20,700/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 1266呎 (3房)
-$2,805万
-$22,158/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$2,789万
-$22,065/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 878呎 (2房)
-$1,809万
-$20,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 887呎 (2房)
-$1,836万
-$20,700/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1266呎 (3房)
-$2,832万
-$22,366/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$2,815万
-$22,272/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 878呎 (2房)
-$1,789万
-$20,380/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 887呎 (2房)
-$1,827万
-$20,600/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 1266呎 (3房)
-$2,804万
-$22,147/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$2,815万
-$22,272/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 878呎 (2房)
-$1,778万
-$20,251/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 887呎 (2房)
-$1,801万
-$20,308/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1266呎 (3房)
-$2,755万
-$21,763/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$2,726万
-$21,562/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1,757万
-$21,741/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1,775万
-$21,964/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 1266呎 (3房)
-$2,720万
-$21,489/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 1380呎 (3房)
-$2,892万
-$20,960/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 878呎 (2房)
-$1,782万
-$20,296/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1,756万
-$21,738/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1266呎 (3房)
-$2,885万
-$22,791/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1380呎 (3房)
-$2,867万
-$20,774/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 878呎 (2房)
-$1,760万
-$20,050/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 887呎 (2房)
-$1,747万
-$19,700/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1266呎 (3房)
-$2,679万
-$21,160/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$2,663万
-$21,071/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 878呎 (2房)
-$1,668万
-$19,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1,774万
-$21,955/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 1388呎 (3房)
-$2,720万
-$19,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 1380呎 (3房)
-$2,705万
-$19,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1,743万
-$21,570/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1,761万
-$21,791/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 1388呎 (3房)
-$2,769万
-$19,950/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$2,839万
-$22,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 878呎 (2房)
-$1,708万
-$19,450/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 887呎 (2房)
-$1,730万
-$19,500/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 1388呎 (3房)
-$2,693万
-$19,400/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$2,677万
-$21,180/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1,710万
-$21,168/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1,762万
-$21,803/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 1266呎 (3房)
-$2,741万
-$21,653/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$2,732万
-$21,617/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1,677万
-$20,755/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 887呎 (2房)
-$1,685万
-$19,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 1250呎 (3房)
-$2,483万
-$19,866/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$2,484万
-$19,652/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 753呎 (2房)
-$1,566万
-$20,797/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 753呎 (2房)
-$1,583万
-$21,019/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>傲玟 - 7座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>47 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>34 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>20&amp;21/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 3236呎 (4+房)
-$11,446万
-$35,371/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 1714呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>19&amp;20/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 2271呎 (4+房)
-$7,508万
-$33,060/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 1352呎 (3房)
-$3,628万
-$26,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,849万
-$23,558/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3,526万
-$26,694/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 1340呎 (3房)
-$3,558万
-$26,551/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,833万
-$23,350/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3,484万
-$26,376/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1340呎 (3房)
-$3,139万
-$23,428/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,798万
-$22,911/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,778万
-$22,644/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3,115万
-$23,584/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 1340呎 (3房)
-$3,136万
-$23,400/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,754万
-$22,340/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3,110万
-$23,544/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,618万
-$20,611/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3,082万
-$23,332/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,598万
-$20,357/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3,050万
-$23,089/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,569万
-$19,985/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3,030万
-$22,940/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 1340呎 (3房)
-$3,030万
-$22,612/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,567万
-$19,963/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,543万
-$19,661/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$2,988万
-$22,621/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1340呎 (3房)
-$2,990万
-$22,313/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,539万
-$19,607/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3,068万
-$23,226/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,526万
-$19,445/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$2,921万
-$22,113/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,522万
-$19,391/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$2,928万
-$22,166/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,509万
-$19,229/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 1385呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1,503万
-$19,142/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-何文田-傲玟.xlsx
+++ b/files/九龙-何文田-傲玟.xlsx
@@ -8,6 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +47,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +153,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +234,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +667,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -19279,4 +19472,4872 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 2357呎 (4+房)
+$7787万
+$33,037/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27&amp;28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 6681呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1442呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2669呎 (4+房)
+$7877万
+$29,514/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$3125万
+$26,347/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3612万
+$26,426/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3618万
+$26,444/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$3002万
+$25,315/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3500万
+$25,604/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3473万
+$25,386/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3454万
+$25,264/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3429万
+$25,069/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3432万
+$25,105/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3742万
+$27,350/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3425万
+$25,052/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3734万
+$27,297/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3417万
+$24,999/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3727万
+$27,244/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3417万
+$24,999/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3340万
+$24,415/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2753万
+$23,210/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3396万
+$24,841/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3321万
+$24,275/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2852万
+$24,050/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3403万
+$24,894/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3313万
+$24,218/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2830万
+$23,860/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$4198万
+$30,710/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3270万
+$23,905/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3374万
+$24,682/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3227万
+$23,588/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2792万
+$23,543/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3665万
+$26,811/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3270万
+$23,905/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+$2815万
+$22,500/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3338万
+$24,418/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3205万
+$23,429/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3330万
+$24,360/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3212万
+$23,482/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3352万
+$24,524/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3209万
+$23,461/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3324万
+$24,312/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3193万
+$23,342/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3604万
+$26,364/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3180万
+$23,246/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3652万
+$26,719/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3154万
+$23,059/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2555万
+$21,539/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1445呎 (3房)
+$4494万
+$31,100/呎
+(20年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3133万
+$22,901/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2540万
+$21,413/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3100万
+$22,677/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 1352呎 (3房)
+$3032万
+$22,423/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2527万
+$21,307/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 2626呎 (4+房)
+$6828万
+$26,000/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr"/>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 2268呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 3461呎 (4+房)
+$12067万
+$34,864/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 2334呎 (4+房)
+$7700万
+$32,991/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2338呎 (4+房)
+$7600万
+$32,506/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1325呎 (3房)
+$3493万
+$26,366/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1347呎 (3房)
+$3548万
+$26,342/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2662万
+$22,561/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1325呎 (3房)
+$3479万
+$26,260/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1347呎 (3房)
+$3491万
+$25,919/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2700万
+$22,881/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$3115万
+$22,200/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$3164万
+$22,200/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1325呎 (3房)
+$3227万
+$24,354/呎
+(24年-02月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1347呎 (3房)
+$3349万
+$24,861/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2995万
+$25,380/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$3073万
+$21,900/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$3121万
+$21,900/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2749万
+$23,299/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$3087万
+$22,000/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1347呎 (3房)
+$3206万
+$23,803/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$3084万
+$26,139/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$3146万
+$22,420/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$3120万
+$21,896/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2608万
+$22,099/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$3199万
+$22,800/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1347呎 (3房)
+$3164万
+$23,486/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2692万
+$22,814/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1325呎 (3房)
+$3115万
+$23,507/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1347呎 (3房)
+$3164万
+$23,486/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2580万
+$21,864/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$3016万
+$21,500/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$2878万
+$20,200/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2532万
+$21,454/呎
+(24年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$4378万
+$31,206/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$2861万
+$20,080/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2488万
+$21,085/呎
+(24年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$2921万
+$20,820/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>B | 1347呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 1244呎 (3房)
+$2513万
+$20,200/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1325呎 (3房)
+$2908万
+$21,947/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$2850万
+$20,000/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2415万
+$20,464/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1325呎 (3房)
+$2868万
+$21,642/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$4225万
+$29,650/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2427万
+$20,570/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 1325呎 (3房)
+$2778万
+$20,966/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 1347呎 (3房)
+$4185万
+$31,066/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2140万
+$18,133/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$4349万
+$31,000/呎
+(19年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$4175万
+$29,295/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2140万
+$18,133/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$4021万
+$28,659/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$4118万
+$28,902/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2132万
+$18,070/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 1325呎 (3房)
+$3934万
+$29,690/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 1347呎 (3房)
+$4086万
+$30,332/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2131万
+$18,059/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$3931万
+$28,018/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$4053万
+$28,445/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2130万
+$18,049/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$3931万
+$28,018/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$4041万
+$28,360/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2128万
+$18,038/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 1325呎 (3房)
+$2804万
+$21,163/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 1330呎 (3房)
+$2800万
+$21,053/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2127万
+$18,027/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr"/>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 2251呎 (4+房)
+$5853万
+$26,000/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 1683呎 (4+房)
+$5471万
+$32,505/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2065呎 (4+房)
+$6250万
+$30,266/呎
+(24年-02月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1978万
+$23,411/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1883万
+$22,280/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 2002呎 (4+房)
+$6254万
+$31,239/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1957万
+$23,157/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1861万
+$22,025/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2677万
+$23,945/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2616万
+$22,689/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1915万
+$22,659/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1840万
+$21,806/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2650万
+$23,703/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2579万
+$22,368/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1943万
+$22,991/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1822万
+$21,584/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2610万
+$23,345/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2558万
+$22,183/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1868万
+$22,107/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1803万
+$21,361/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2892万
+$25,867/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2535万
+$21,987/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1840万
+$21,775/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1784万
+$21,139/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2560万
+$22,898/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2535万
+$21,987/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1905万
+$22,549/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1765万
+$20,916/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2542万
+$22,737/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2870万
+$24,892/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1882万
+$22,272/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1728万
+$20,471/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2535万
+$22,674/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2497万
+$21,660/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1873万
+$22,162/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1765万
+$20,916/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2505万
+$22,407/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2491万
+$21,606/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1857万
+$21,974/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1708万
+$20,237/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2493万
+$22,297/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2465万
+$21,379/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1840万
+$21,775/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1694万
+$20,071/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2473万
+$22,122/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2450万
+$21,249/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1831万
+$21,664/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1690万
+$20,026/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2456万
+$21,968/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2426万
+$21,040/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1812万
+$21,443/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1662万
+$19,692/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1228呎 (3房)
+$3616万
+$29,450/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2428万
+$21,062/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1804万
+$21,344/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1657万
+$19,637/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2438万
+$21,803/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2428万
+$21,062/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1800万
+$21,302/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1653万
+$19,581/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2419万
+$21,638/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2397万
+$20,789/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 934呎 (2房)
+$2852万
+$30,538/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1648万
+$19,525/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1228呎 (3房)
+$3513万
+$28,610/呎
+(20年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2384万
+$20,676/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$2824万
+$33,422/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 939呎 (2房)
+$2644万
+$28,160/呎
+(20年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2395万
+$21,419/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2359万
+$20,460/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1775万
+$21,001/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1624万
+$19,247/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2368万
+$21,177/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2297万
+$19,919/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1765万
+$20,891/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1620万
+$19,192/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2364万
+$21,144/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2297万
+$19,919/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1763万
+$20,869/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1619万
+$19,181/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2337万
+$20,902/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2290万
+$19,864/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1756万
+$20,780/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1619万
+$19,181/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 1118呎 (3房)
+$2313万
+$20,691/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$2284万
+$19,810/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 829呎 (2房)
+$1726万
+$20,818/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 844呎 (2房)
+$1618万
+$19,169/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>20&amp;21</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 3100呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 1747呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 1691呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 898呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 892呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+$2065万
+$23,200/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 892呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+$2031万
+$22,820/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 892呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2011万
+$24,740/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 892呎 (2房)
+$1962万
+$22,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2003万
+$24,637/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 892呎 (2房)
+$1953万
+$21,900/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1878万
+$23,098/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1838万
+$22,630/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1863万
+$22,912/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1829万
+$22,520/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1927万
+$23,700/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1882万
+$23,177/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1829万
+$22,496/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1797万
+$22,135/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1816万
+$22,332/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1793万
+$22,080/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1798万
+$22,113/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 892呎 (2房)
+$1869万
+$20,950/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+$1860万
+$20,900/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1860万
+$22,904/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 892呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 892呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 1595呎 (4+房)
+$4779万
+$29,964/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1924万
+$23,811/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1934万
+$23,931/呎
+(24年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>20&amp;21</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 2905呎 (4+房)
+$9870万
+$33,976/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2258呎 (4+房)
+$7128万
+$31,568/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$3021万
+$23,902/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1912万
+$23,663/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1916万
+$23,712/呎
+(24年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1266呎 (3房)
+$3067万
+$24,230/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$3043万
+$24,074/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1883万
+$23,308/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1903万
+$23,547/呎
+(24年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1266呎 (3房)
+$2983万
+$23,562/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$2891万
+$22,873/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 878呎 (2房)
+$1844万
+$21,000/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 887呎 (2房)
+$1836万
+$20,700/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1266呎 (3房)
+$2805万
+$22,158/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$2789万
+$22,065/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 878呎 (2房)
+$1809万
+$20,600/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 887呎 (2房)
+$1836万
+$20,700/呎
+(23年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1266呎 (3房)
+$2832万
+$22,366/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$2815万
+$22,272/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 878呎 (2房)
+$1789万
+$20,380/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 887呎 (2房)
+$1827万
+$20,600/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1266呎 (3房)
+$2804万
+$22,147/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$2815万
+$22,272/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 878呎 (2房)
+$1778万
+$20,251/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 887呎 (2房)
+$1801万
+$20,308/呎
+(23年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1266呎 (3房)
+$2755万
+$21,763/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$2726万
+$21,562/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1757万
+$21,741/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1775万
+$21,964/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1266呎 (3房)
+$2720万
+$21,489/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1380呎 (3房)
+$2892万
+$20,960/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 878呎 (2房)
+$1782万
+$20,296/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1756万
+$21,738/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1266呎 (3房)
+$2885万
+$22,791/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1380呎 (3房)
+$2867万
+$20,774/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 878呎 (2房)
+$1760万
+$20,050/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 887呎 (2房)
+$1747万
+$19,700/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1266呎 (3房)
+$2679万
+$21,160/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$2663万
+$21,071/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 878呎 (2房)
+$1668万
+$19,000/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1774万
+$21,955/呎
+(23年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1388呎 (3房)
+$2720万
+$19,600/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1380呎 (3房)
+$2705万
+$19,600/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1743万
+$21,570/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1761万
+$21,791/呎
+(23年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1388呎 (3房)
+$2769万
+$19,950/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$2839万
+$22,462/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 878呎 (2房)
+$1708万
+$19,450/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 887呎 (2房)
+$1730万
+$19,500/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1388呎 (3房)
+$2693万
+$19,400/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$2677万
+$21,180/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1710万
+$21,168/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1762万
+$21,803/呎
+(23年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 1266呎 (3房)
+$2741万
+$21,653/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$2732万
+$21,617/呎
+(24年-02月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1677万
+$20,755/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 887呎 (2房)
+$1685万
+$19,000/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 1250呎 (3房)
+$2483万
+$19,866/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$2484万
+$19,652/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 753呎 (2房)
+$1566万
+$20,797/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 753呎 (2房)
+$1583万
+$21,019/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>7座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>20&amp;21</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 3236呎 (4+房)
+$11446万
+$35,371/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 1714呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2271呎 (4+房)
+$7508万
+$33,060/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1352呎 (3房)
+$3628万
+$26,833/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1849万
+$23,558/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3526万
+$26,694/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1340呎 (3房)
+$3558万
+$26,551/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1833万
+$23,350/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3484万
+$26,376/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1340呎 (3房)
+$3139万
+$23,428/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1798万
+$22,911/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1778万
+$22,644/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3115万
+$23,584/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1340呎 (3房)
+$3136万
+$23,400/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1754万
+$22,340/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3110万
+$23,544/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1618万
+$20,611/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3082万
+$23,332/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1598万
+$20,357/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3050万
+$23,089/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1569万
+$19,985/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3030万
+$22,940/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1340呎 (3房)
+$3030万
+$22,612/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1567万
+$19,963/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1543万
+$19,661/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$2988万
+$22,621/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1340呎 (3房)
+$2990万
+$22,313/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1539万
+$19,607/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3068万
+$23,226/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1526万
+$19,445/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$2921万
+$22,113/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1522万
+$19,391/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$2928万
+$22,166/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1509万
+$19,229/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1385呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1503万
+$19,142/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-何文田-傲玟.xlsx
+++ b/files/九龙-何文田-傲玟.xlsx
@@ -667,7 +667,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -20452,10 +20452,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
@@ -20463,32 +20487,8 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/九龙-何文田-傲玟.xlsx
+++ b/files/九龙-何文田-傲玟.xlsx
@@ -27654,10 +27654,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1442呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 6681呎 (4+房)
 -
@@ -27665,32 +27689,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1442呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28504,10 +28504,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
@@ -28515,32 +28539,8 @@
 (24年-04月-08日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月-11日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31133,11 +31133,36 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1924万
+$23,811/呎
+(24年-03月-17日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1934万
+$23,931/呎
+(24年-02月-01日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20&amp;21</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 2905呎 (4+房)
 $9870万
@@ -31145,33 +31170,8 @@
 (26年-04月-12日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1924万
-$23,811/呎
-(24年-03月-17日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1934万
-$23,931/呎
-(24年-02月-01日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/九龙-何文田-傲玟.xlsx
+++ b/files/九龙-何文田-傲玟.xlsx
@@ -27654,11 +27654,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 6681呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1442呎 (1房)
 -
@@ -27666,7 +27683,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27674,23 +27691,6 @@
 (待售)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 6681呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31176,10 +31176,42 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$3021万
+$23,902/呎
+(25年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1912万
+$23,663/呎
+(24年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1916万
+$23,712/呎
+(24年-01月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 2258呎 (4+房)
 $7128万
@@ -31187,41 +31219,9 @@
 (26年-01月-26日)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr"/>
-      <c r="E8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$3021万
-$23,902/呎
-(25年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1912万
-$23,663/呎
-(24年-03月-21日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1916万
-$23,712/呎
-(24年-01月-11日)</t>
-        </is>
-      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">

--- a/files/九龙-何文田-傲玟.xlsx
+++ b/files/九龙-何文田-傲玟.xlsx
@@ -131,6 +131,11 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -139,11 +144,6 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -291,13 +291,13 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16605,7 +16605,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -16615,12 +16615,12 @@
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J241" s="3" t="inlineStr">
@@ -16630,12 +16630,12 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -16891,12 +16891,12 @@
       </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I245" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J245" s="3" t="inlineStr">
@@ -16906,12 +16906,12 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>892</v>
+        <v>812</v>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
@@ -17162,14 +17162,14 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
         <v>19624000</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>22000</v>
+        <v>24167</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         </is>
       </c>
       <c r="E282" s="4" t="n">
-        <v>890</v>
+        <v>813</v>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
@@ -19404,14 +19404,14 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
         <v>18601000</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>20900</v>
+        <v>22879</v>
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
@@ -19675,23 +19675,19 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H286" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I286" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H286" s="5" t="n">
+        <v>18645500</v>
+      </c>
+      <c r="I286" s="5" t="n">
+        <v>20950</v>
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
@@ -19700,12 +19696,12 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
@@ -19715,7 +19711,7 @@
       </c>
       <c r="N286" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26393,23 +26389,19 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H387" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I387" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H387" s="5" t="n">
+        <v>31413000</v>
+      </c>
+      <c r="I387" s="5" t="n">
+        <v>22200</v>
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
@@ -26418,12 +26410,12 @@
       </c>
       <c r="K387" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M387" s="3" t="inlineStr">
@@ -26433,7 +26425,7 @@
       </c>
       <c r="N387" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26463,23 +26455,19 @@
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H388" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I388" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H388" s="5" t="n">
+        <v>35122500</v>
+      </c>
+      <c r="I388" s="5" t="n">
+        <v>25070</v>
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
@@ -26488,12 +26476,12 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M388" s="3" t="inlineStr">
@@ -26503,7 +26491,7 @@
       </c>
       <c r="N388" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27588,27 +27576,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27819,38 @@
 (25年-03月-13日)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3425万
+$25,052/呎
+(24年-12月-05日)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3734万
+$27,297/呎
+(25年-03月-13日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27840,29 +27859,246 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3425万
-$25,052/呎
-(24年-12月-05日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
+$3417万
+$24,999/呎
+(24年-12月-15日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3734万
-$27,297/呎
-(25年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+$3727万
+$27,244/呎
+(25年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3417万
+$24,999/呎
+(24年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3340万
+$24,415/呎
+(25年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2753万
+$23,210/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3396万
+$24,841/呎
+(24年-11月-20日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3321万
+$24,275/呎
+(25年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2852万
+$24,050/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3403万
+$24,894/呎
+(24年-12月-23日)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3313万
+$24,218/呎
+(25年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2830万
+$23,860/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$4198万
+$30,710/呎
+(26年-02月-09日)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3270万
+$23,905/呎
+(25年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3374万
+$24,682/呎
+(25年-01月-02日)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3227万
+$23,588/呎
+(24年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2792万
+$23,543/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3665万
+$26,811/呎
+(25年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3270万
+$23,905/呎
+(26年-04月-19日)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+$2815万
+$22,500/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3338万
+$24,418/呎
+(25年-11月-19日)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3205万
+$23,429/呎
+(25年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27871,29 +28107,29 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3417万
-$24,999/呎
-(24年-12月-15日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
+$3330万
+$24,360/呎
+(25年-11月-18日)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3727万
-$27,244/呎
-(25年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
+$3212万
+$23,482/呎
+(26年-03月-29日)</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -27902,122 +28138,29 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3417万
-$24,999/呎
-(24年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+$3352万
+$24,524/呎
+(25年-12月-16日)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3340万
-$24,415/呎
-(25年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2753万
-$23,210/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3396万
-$24,841/呎
-(24年-11月-20日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3321万
-$24,275/呎
-(25年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2852万
-$24,050/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3403万
-$24,894/呎
-(24年-12月-23日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3313万
-$24,218/呎
-(25年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2830万
-$23,860/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$4198万
-$30,710/呎
-(26年-02月-09日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3270万
-$23,905/呎
-(25年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
+$3209万
+$23,461/呎
+(26年-04月-12日)</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -28026,91 +28169,29 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3374万
-$24,682/呎
-(25年-01月-02日)</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
+$3324万
+$24,312/呎
+(24年-04月-11日)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3227万
-$23,588/呎
-(24年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2792万
-$23,543/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3665万
-$26,811/呎
-(25年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3270万
-$23,905/呎
-(26年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-$2815万
-$22,500/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3338万
-$24,418/呎
-(25年-11月-19日)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3205万
-$23,429/呎
-(25年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
+$3193万
+$23,342/呎
+(24年-04月-07日)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -28119,127 +28200,34 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3330万
-$24,360/呎
-(25年-11月-18日)</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
+$3604万
+$26,364/呎
+(25年-02月-16日)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3212万
-$23,482/呎
-(26年-03月-29日)</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
+$3180万
+$23,246/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
 -
 (在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3352万
-$24,524/呎
-(25年-12月-16日)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3209万
-$23,461/呎
-(26年-04月-12日)</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3324万
-$24,312/呎
-(24年-04月-11日)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3193万
-$23,342/呎
-(24年-04月-07日)</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3604万
-$26,364/呎
-(25年-02月-16日)</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3180万
-$23,246/呎
-(26年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
         </is>
       </c>
     </row>
@@ -28504,11 +28492,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2338呎 (4+房)
+$7600万
+$32,506/呎
+(24年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1351呎 (3房)
 $3630万
@@ -28516,7 +28521,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1180呎 (3房)
 $2612万
@@ -28525,23 +28530,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2338呎 (4+房)
-$7600万
-$32,506/呎
-(24年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -28897,7 +28885,7 @@
 (23年-11月-08日)</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>B | 1347呎 (3房)
 -
@@ -29354,10 +29342,35 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
@@ -29365,34 +29378,9 @@
 (25年-02月-25日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30310,17 +30298,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30330,7 +30318,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -30512,12 +30500,12 @@
 (26年-07月-05日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30551,12 +30539,12 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30592,10 +30580,10 @@
       </c>
       <c r="E11" s="21" t="inlineStr">
         <is>
-          <t>D | 892呎 (2房)
+          <t>D | 812呎 (2房)
 $1962万
-$22,000/呎
-(26年-06月-21日)</t>
+$24,167/呎
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -30896,10 +30884,10 @@
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>C | 890呎 (2房)
+          <t>C | 813呎 (2房)
 $1860万
-$20,900/呎
-(26年-06月-11日)</t>
+$22,879/呎
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -30933,12 +30921,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
-招标单位
--
-(已定价未售)</t>
+$1865万
+$20,950/呎
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -31133,12 +31121,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20&amp;21</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2905呎 (4+房)
+$9870万
+$33,976/呎
+(26年-04月-12日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1924万
@@ -31146,7 +31152,7 @@
 (24年-03月-17日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1934万
@@ -31155,32 +31161,32 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20&amp;21</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 2905呎 (4+房)
-$9870万
-$33,976/呎
-(26年-04月-12日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2258呎 (4+房)
+$7128万
+$31,568/呎
+(26年-01月-26日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 1264呎 (3房)
 $3021万
@@ -31188,7 +31194,7 @@
 (25年-10月-07日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1912万
@@ -31196,7 +31202,7 @@
 (24年-03月-21日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1916万
@@ -31204,24 +31210,6 @@
 (24年-01月-11日)</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 2258呎 (4+房)
-$7128万
-$31,568/呎
-(26年-01月-26日)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31845,12 +31833,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32089,7 +32077,7 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
@@ -32120,7 +32108,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
@@ -32151,7 +32139,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
@@ -32205,20 +32193,20 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 1401呎 (3房)
-招标单位
--
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
+$3512万
+$25,070/呎
+(26年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
-招标单位
--
-(已定价未售)</t>
+$3141万
+$22,200/呎
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -32275,7 +32263,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
@@ -32306,7 +32294,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
@@ -32337,7 +32325,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位

--- a/files/九龙-何文田-傲玟.xlsx
+++ b/files/九龙-何文田-傲玟.xlsx
@@ -19338,7 +19338,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -27635,17 +27635,41 @@
           <t>C | 2357呎 (4+房)
 $7787万
 $33,037/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1442呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 6681呎 (4+房)
 -
@@ -27653,25 +27677,87 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1442呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2669呎 (4+房)
+$7877万
+$29,514/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$3125万
+$26,347/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3612万
+$26,426/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3618万
+$26,444/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$3002万
+$25,315/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3500万
+$25,604/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3473万
+$25,386/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27680,84 +27766,29 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 2669呎 (4+房)
-$7877万
-$29,514/呎
-(25年-03月-12日)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$3125万
-$26,347/呎
-(26年-01月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3612万
-$26,426/呎
-(24年-07月-25日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
+$3454万
+$25,264/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3618万
-$26,444/呎
-(24年-07月-25日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$3002万
-$25,315/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3500万
-$25,604/呎
-(24年-10月-09日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3473万
-$25,386/呎
-(24年-12月-23日)</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
+$3429万
+$25,069/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27766,29 +27797,60 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3454万
-$25,264/呎
-(25年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
+$3432万
+$25,105/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3429万
-$25,069/呎
-(25年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
+$3742万
+$27,350/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3425万
+$25,052/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3734万
+$27,297/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27797,60 +27859,246 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3432万
-$25,105/呎
-(24年-12月-15日)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
+$3417万
+$24,999/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3742万
-$27,350/呎
-(25年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
+$3727万
+$27,244/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3425万
-$25,052/呎
-(24年-12月-05日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
+$3417万
+$24,999/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3734万
-$27,297/呎
-(25年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+$3340万
+$24,415/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2753万
+$23,210/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3396万
+$24,841/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3321万
+$24,275/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2852万
+$24,050/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3403万
+$24,894/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3313万
+$24,218/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2830万
+$23,860/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$4198万
+$30,710/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3270万
+$23,905/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3374万
+$24,682/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3227万
+$23,588/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2792万
+$23,543/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3665万
+$26,811/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3270万
+$23,905/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+$2815万
+$22,500/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3338万
+$24,418/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3205万
+$23,429/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27859,29 +28107,29 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3417万
-$24,999/呎
-(24年-12月-15日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
+$3330万
+$24,360/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3727万
-$27,244/呎
-(25年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
+$3212万
+$23,482/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -27890,122 +28138,29 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3417万
-$24,999/呎
-(24年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+$3352万
+$24,524/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3340万
-$24,415/呎
-(25年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2753万
-$23,210/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3396万
-$24,841/呎
-(24年-11月-20日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3321万
-$24,275/呎
-(25年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2852万
-$24,050/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3403万
-$24,894/呎
-(24年-12月-23日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3313万
-$24,218/呎
-(25年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2830万
-$23,860/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$4198万
-$30,710/呎
-(26年-02月-09日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3270万
-$23,905/呎
-(25年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
+$3209万
+$23,461/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -28014,91 +28169,29 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3374万
-$24,682/呎
-(25年-01月-02日)</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
+$3324万
+$24,312/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3227万
-$23,588/呎
-(24年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2792万
-$23,543/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3665万
-$26,811/呎
-(25年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3270万
-$23,905/呎
-(26年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-$2815万
-$22,500/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3338万
-$24,418/呎
-(25年-11月-19日)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3205万
-$23,429/呎
-(25年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
+$3193万
+$23,342/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -28107,29 +28200,29 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3330万
-$24,360/呎
-(25年-11月-18日)</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
+$3604万
+$26,364/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3212万
-$23,482/呎
-(26年-03月-29日)</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
+$3180万
+$23,246/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -28138,99 +28231,6 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3352万
-$24,524/呎
-(25年-12月-16日)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3209万
-$23,461/呎
-(26年-04月-12日)</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3324万
-$24,312/呎
-(24年-04月-11日)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3193万
-$23,342/呎
-(24年-04月-07日)</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3604万
-$26,364/呎
-(25年-02月-16日)</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3180万
-$23,246/呎
-(26年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
           <t>A | 1367呎 (3房)
 $3652万
 $26,719/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -28250,7 +28250,7 @@
           <t>B | 1368呎 (3房)
 $3154万
 $23,059/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -28258,7 +28258,7 @@
           <t>C | 1186呎 (3房)
 $2555万
 $21,539/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -28273,7 +28273,7 @@
           <t>A | 1445呎 (3房)
 $4494万
 $31,100/呎
-(20年-06月-18日)</t>
+(20年-06月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -28281,7 +28281,7 @@
           <t>B | 1368呎 (3房)
 $3133万
 $22,901/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -28289,7 +28289,7 @@
           <t>C | 1186呎 (3房)
 $2540万
 $21,413/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -28304,7 +28304,7 @@
           <t>A | 1367呎 (3房)
 $3100万
 $22,677/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -28312,7 +28312,7 @@
           <t>B | 1352呎 (3房)
 $3032万
 $22,423/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -28320,7 +28320,7 @@
           <t>C | 1186呎 (3房)
 $2527万
 $21,307/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
           <t>A | 2626呎 (4+房)
 $6828万
 $26,000/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr"/>
@@ -28477,7 +28477,7 @@
           <t>B | 3461呎 (4+房)
 $12067万
 $34,864/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -28485,141 +28485,141 @@
           <t>C | 2334呎 (4+房)
 $7700万
 $32,991/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
 $32,506/呎
-(24年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1325呎 (3房)
+$3493万
+$26,366/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1347呎 (3房)
+$3548万
+$26,342/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2662万
+$22,561/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1325呎 (3房)
+$3479万
+$26,260/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1347呎 (3房)
+$3491万
+$25,919/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2700万
+$22,881/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1403呎 (3房)
+$3115万
+$22,200/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1425呎 (3房)
+$3164万
+$22,200/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 1180呎 (3房)
 $2612万
 $22,139/呎
-(25年-09月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 1325呎 (3房)
-$3493万
-$26,366/呎
-(24年-01月-24日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 1347呎 (3房)
-$3548万
-$26,342/呎
-(24年-01月-25日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2662万
-$22,561/呎
-(26年-04月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 1325呎 (3房)
-$3479万
-$26,260/呎
-(23年-11月-30日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 1347呎 (3房)
-$3491万
-$25,919/呎
-(23年-10月-16日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2700万
-$22,881/呎
-(24年-09月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 1403呎 (3房)
-$3115万
-$22,200/呎
-(23年-10月-17日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 1425呎 (3房)
-$3164万
-$22,200/呎
-(23年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(24年-08月-22日)</t>
+(24年-08月)</t>
         </is>
       </c>
     </row>
@@ -28634,7 +28634,7 @@
           <t>A | 1325呎 (3房)
 $3227万
 $24,354/呎
-(24年-02月-05日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -28642,7 +28642,7 @@
           <t>B | 1347呎 (3房)
 $3349万
 $24,861/呎
-(23年-11月-29日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -28650,7 +28650,7 @@
           <t>C | 1180呎 (3房)
 $2995万
 $25,380/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -28665,7 +28665,7 @@
           <t>A | 1403呎 (3房)
 $3073万
 $21,900/呎
-(23年-10月-16日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -28673,7 +28673,7 @@
           <t>B | 1425呎 (3房)
 $3121万
 $21,900/呎
-(23年-10月-23日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -28681,7 +28681,7 @@
           <t>C | 1180呎 (3房)
 $2749万
 $23,299/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -28696,7 +28696,7 @@
           <t>A | 1403呎 (3房)
 $3087万
 $22,000/呎
-(23年-10月-30日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -28704,7 +28704,7 @@
           <t>B | 1347呎 (3房)
 $3206万
 $23,803/呎
-(23年-12月-11日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -28712,7 +28712,7 @@
           <t>C | 1180呎 (3房)
 $3084万
 $26,139/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -28727,7 +28727,7 @@
           <t>A | 1403呎 (3房)
 $3146万
 $22,420/呎
-(23年-11月-13日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -28735,7 +28735,7 @@
           <t>B | 1425呎 (3房)
 $3120万
 $21,896/呎
-(23年-10月-18日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -28743,7 +28743,7 @@
           <t>C | 1180呎 (3房)
 $2608万
 $22,099/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -28758,7 +28758,7 @@
           <t>A | 1403呎 (3房)
 $3199万
 $22,800/呎
-(23年-10月-17日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -28766,7 +28766,7 @@
           <t>B | 1347呎 (3房)
 $3164万
 $23,486/呎
-(24年-01月-02日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -28774,7 +28774,7 @@
           <t>C | 1180呎 (3房)
 $2692万
 $22,814/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -28789,7 +28789,7 @@
           <t>A | 1325呎 (3房)
 $3115万
 $23,507/呎
-(23年-11月-29日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -28797,7 +28797,7 @@
           <t>B | 1347呎 (3房)
 $3164万
 $23,486/呎
-(24年-08月-04日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -28805,7 +28805,7 @@
           <t>C | 1180呎 (3房)
 $2580万
 $21,864/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -28820,7 +28820,7 @@
           <t>A | 1403呎 (3房)
 $3016万
 $21,500/呎
-(23年-10月-17日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -28828,7 +28828,7 @@
           <t>B | 1425呎 (3房)
 $2878万
 $20,200/呎
-(23年-10月-12日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -28836,7 +28836,7 @@
           <t>C | 1180呎 (3房)
 $2532万
 $21,454/呎
-(24年-03月-05日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -28851,7 +28851,7 @@
           <t>A | 1403呎 (3房)
 $4378万
 $31,206/呎
-(20年-05月-17日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -28859,7 +28859,7 @@
           <t>B | 1425呎 (3房)
 $2861万
 $20,080/呎
-(23年-10月-05日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -28867,7 +28867,7 @@
           <t>C | 1180呎 (3房)
 $2488万
 $21,085/呎
-(24年-01月-28日)</t>
+(24年-01月)</t>
         </is>
       </c>
     </row>
@@ -28882,7 +28882,7 @@
           <t>A | 1403呎 (3房)
 $2921万
 $20,820/呎
-(23年-11月-08日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
@@ -28898,7 +28898,7 @@
           <t>C | 1244呎 (3房)
 $2513万
 $20,200/呎
-(23年-10月-18日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -28913,7 +28913,7 @@
           <t>A | 1325呎 (3房)
 $2908万
 $21,947/呎
-(23年-12月-06日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -28921,7 +28921,7 @@
           <t>B | 1425呎 (3房)
 $2850万
 $20,000/呎
-(23年-10月-30日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -28929,7 +28929,7 @@
           <t>C | 1180呎 (3房)
 $2415万
 $20,464/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -28944,7 +28944,7 @@
           <t>A | 1325呎 (3房)
 $2868万
 $21,642/呎
-(23年-12月-05日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -28952,7 +28952,7 @@
           <t>B | 1425呎 (3房)
 $4225万
 $29,650/呎
-(20年-05月-27日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -28960,7 +28960,7 @@
           <t>C | 1180呎 (3房)
 $2427万
 $20,570/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
           <t>A | 1325呎 (3房)
 $2778万
 $20,966/呎
-(23年-10月-16日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -28983,7 +28983,7 @@
           <t>B | 1347呎 (3房)
 $4185万
 $31,066/呎
-(20年-05月-17日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -28991,7 +28991,7 @@
           <t>C | 1180呎 (3房)
 $2140万
 $18,133/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -29006,7 +29006,7 @@
           <t>A | 1403呎 (3房)
 $4349万
 $31,000/呎
-(19年-12月-11日)</t>
+(19年-12月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -29014,7 +29014,7 @@
           <t>B | 1425呎 (3房)
 $4175万
 $29,295/呎
-(20年-05月-14日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -29022,7 +29022,7 @@
           <t>C | 1180呎 (3房)
 $2140万
 $18,133/呎
-(26年-01月-01日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -29037,7 +29037,7 @@
           <t>A | 1403呎 (3房)
 $4021万
 $28,659/呎
-(20年-05月-25日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -29045,7 +29045,7 @@
           <t>B | 1425呎 (3房)
 $4118万
 $28,902/呎
-(20年-05月-14日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -29053,7 +29053,7 @@
           <t>C | 1180呎 (3房)
 $2132万
 $18,070/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -29068,7 +29068,7 @@
           <t>A | 1325呎 (3房)
 $3934万
 $29,690/呎
-(20年-05月-17日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -29076,7 +29076,7 @@
           <t>B | 1347呎 (3房)
 $4086万
 $30,332/呎
-(20年-05月-17日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -29084,7 +29084,7 @@
           <t>C | 1180呎 (3房)
 $2131万
 $18,059/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -29099,7 +29099,7 @@
           <t>A | 1403呎 (3房)
 $3931万
 $28,018/呎
-(20年-05月-19日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -29107,7 +29107,7 @@
           <t>B | 1425呎 (3房)
 $4053万
 $28,445/呎
-(20年-05月-27日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -29115,7 +29115,7 @@
           <t>C | 1180呎 (3房)
 $2130万
 $18,049/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -29130,7 +29130,7 @@
           <t>A | 1403呎 (3房)
 $3931万
 $28,018/呎
-(21年-03月-30日)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -29138,7 +29138,7 @@
           <t>B | 1425呎 (3房)
 $4041万
 $28,360/呎
-(20年-12月-23日)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -29146,7 +29146,7 @@
           <t>C | 1180呎 (3房)
 $2128万
 $18,038/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -29161,7 +29161,7 @@
           <t>A | 1325呎 (3房)
 $2804万
 $21,163/呎
-(24年-01月-16日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -29169,7 +29169,7 @@
           <t>B | 1330呎 (3房)
 $2800万
 $21,053/呎
-(24年-01月-18日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -29177,7 +29177,7 @@
           <t>C | 1180呎 (3房)
 $2127万
 $18,027/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -29194,7 +29194,7 @@
           <t>C | 2251呎 (4+房)
 $5853万
 $26,000/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -29334,7 +29334,7 @@
           <t>C | 1683呎 (4+房)
 $5471万
 $32,505/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr"/>
@@ -29342,45 +29342,45 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
 $1984万
 $23,479/呎
-(25年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 845呎 (2房)
 $1873万
 $22,169/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-25日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
+(25年-07月)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29393,7 +29393,7 @@
           <t>A | 2065呎 (4+房)
 $6250万
 $30,266/呎
-(24年-02月-01日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
@@ -29402,7 +29402,7 @@
           <t>C | 845呎 (2房)
 $1978万
 $23,411/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -29410,7 +29410,7 @@
           <t>D | 845呎 (2房)
 $1883万
 $22,280/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -29425,7 +29425,7 @@
           <t>A | 2002呎 (4+房)
 $6254万
 $31,239/呎
-(24年-03月-04日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -29434,7 +29434,7 @@
           <t>C | 845呎 (2房)
 $1957万
 $23,157/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -29442,7 +29442,7 @@
           <t>D | 845呎 (2房)
 $1861万
 $22,025/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -29457,7 +29457,7 @@
           <t>A | 1118呎 (3房)
 $2677万
 $23,945/呎
-(26年-03月-19日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -29465,7 +29465,7 @@
           <t>B | 1153呎 (3房)
 $2616万
 $22,689/呎
-(24年-10月-14日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -29473,7 +29473,7 @@
           <t>C | 845呎 (2房)
 $1915万
 $22,659/呎
-(24年-08月-29日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -29481,7 +29481,7 @@
           <t>D | 844呎 (2房)
 $1840万
 $21,806/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -29496,7 +29496,7 @@
           <t>A | 1118呎 (3房)
 $2650万
 $23,703/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -29504,7 +29504,7 @@
           <t>B | 1153呎 (3房)
 $2579万
 $22,368/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -29512,7 +29512,7 @@
           <t>C | 845呎 (2房)
 $1943万
 $22,991/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -29520,7 +29520,7 @@
           <t>D | 844呎 (2房)
 $1822万
 $21,584/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -29535,7 +29535,7 @@
           <t>A | 1118呎 (3房)
 $2610万
 $23,345/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -29543,7 +29543,7 @@
           <t>B | 1153呎 (3房)
 $2558万
 $22,183/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -29551,7 +29551,7 @@
           <t>C | 845呎 (2房)
 $1868万
 $22,107/呎
-(25年-06月-01日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -29559,7 +29559,7 @@
           <t>D | 844呎 (2房)
 $1803万
 $21,361/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
           <t>A | 1118呎 (3房)
 $2892万
 $25,867/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -29582,7 +29582,7 @@
           <t>B | 1153呎 (3房)
 $2535万
 $21,987/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -29590,7 +29590,7 @@
           <t>C | 845呎 (2房)
 $1840万
 $21,775/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -29598,7 +29598,7 @@
           <t>D | 844呎 (2房)
 $1784万
 $21,139/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -29613,7 +29613,7 @@
           <t>A | 1118呎 (3房)
 $2560万
 $22,898/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -29621,7 +29621,7 @@
           <t>B | 1153呎 (3房)
 $2535万
 $21,987/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -29629,7 +29629,7 @@
           <t>C | 845呎 (2房)
 $1905万
 $22,549/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -29637,7 +29637,7 @@
           <t>D | 844呎 (2房)
 $1765万
 $20,916/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -29652,7 +29652,7 @@
           <t>A | 1118呎 (3房)
 $2542万
 $22,737/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -29660,7 +29660,7 @@
           <t>B | 1153呎 (3房)
 $2870万
 $24,892/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -29668,7 +29668,7 @@
           <t>C | 845呎 (2房)
 $1882万
 $22,272/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -29676,7 +29676,7 @@
           <t>D | 844呎 (2房)
 $1728万
 $20,471/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -29691,7 +29691,7 @@
           <t>A | 1118呎 (3房)
 $2535万
 $22,674/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -29699,7 +29699,7 @@
           <t>B | 1153呎 (3房)
 $2497万
 $21,660/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -29707,7 +29707,7 @@
           <t>C | 845呎 (2房)
 $1873万
 $22,162/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -29715,7 +29715,7 @@
           <t>D | 844呎 (2房)
 $1765万
 $20,916/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -29730,7 +29730,7 @@
           <t>A | 1118呎 (3房)
 $2505万
 $22,407/呎
-(25年-10月-30日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -29738,7 +29738,7 @@
           <t>B | 1153呎 (3房)
 $2491万
 $21,606/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -29746,7 +29746,7 @@
           <t>C | 845呎 (2房)
 $1857万
 $21,974/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -29754,7 +29754,7 @@
           <t>D | 844呎 (2房)
 $1708万
 $20,237/呎
-(24年-12月-18日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -29769,7 +29769,7 @@
           <t>A | 1118呎 (3房)
 $2493万
 $22,297/呎
-(25年-07月-27日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -29777,7 +29777,7 @@
           <t>B | 1153呎 (3房)
 $2465万
 $21,379/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -29785,7 +29785,7 @@
           <t>C | 845呎 (2房)
 $1840万
 $21,775/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -29793,7 +29793,7 @@
           <t>D | 844呎 (2房)
 $1694万
 $20,071/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -29808,7 +29808,7 @@
           <t>A | 1118呎 (3房)
 $2473万
 $22,122/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -29816,7 +29816,7 @@
           <t>B | 1153呎 (3房)
 $2450万
 $21,249/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -29824,7 +29824,7 @@
           <t>C | 845呎 (2房)
 $1831万
 $21,664/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -29832,7 +29832,7 @@
           <t>D | 844呎 (2房)
 $1690万
 $20,026/呎
-(24年-08月-08日)</t>
+(24年-08月)</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
           <t>A | 1118呎 (3房)
 $2456万
 $21,968/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -29855,7 +29855,7 @@
           <t>B | 1153呎 (3房)
 $2426万
 $21,040/呎
-(25年-11月-02日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -29863,7 +29863,7 @@
           <t>C | 845呎 (2房)
 $1812万
 $21,443/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -29871,7 +29871,7 @@
           <t>D | 844呎 (2房)
 $1662万
 $19,692/呎
-(25年-02月-20日)</t>
+(25年-02月)</t>
         </is>
       </c>
     </row>
@@ -29886,7 +29886,7 @@
           <t>A | 1228呎 (3房)
 $3616万
 $29,450/呎
-(20年-07月-27日)</t>
+(20年-07月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -29894,7 +29894,7 @@
           <t>B | 1153呎 (3房)
 $2428万
 $21,062/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -29902,7 +29902,7 @@
           <t>C | 845呎 (2房)
 $1804万
 $21,344/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -29910,7 +29910,7 @@
           <t>D | 844呎 (2房)
 $1657万
 $19,637/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -29925,7 +29925,7 @@
           <t>A | 1118呎 (3房)
 $2438万
 $21,803/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -29933,7 +29933,7 @@
           <t>B | 1153呎 (3房)
 $2428万
 $21,062/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -29941,7 +29941,7 @@
           <t>C | 845呎 (2房)
 $1800万
 $21,302/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -29949,7 +29949,7 @@
           <t>D | 844呎 (2房)
 $1653万
 $19,581/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -29964,7 +29964,7 @@
           <t>A | 1118呎 (3房)
 $2419万
 $21,638/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -29972,7 +29972,7 @@
           <t>B | 1153呎 (3房)
 $2397万
 $20,789/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -29980,7 +29980,7 @@
           <t>C | 934呎 (2房)
 $2852万
 $30,538/呎
-(20年-07月-21日)</t>
+(20年-07月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -29988,7 +29988,7 @@
           <t>D | 844呎 (2房)
 $1648万
 $19,525/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -30003,7 +30003,7 @@
           <t>A | 1228呎 (3房)
 $3513万
 $28,610/呎
-(20年-06月-11日)</t>
+(20年-06月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -30011,7 +30011,7 @@
           <t>B | 1153呎 (3房)
 $2384万
 $20,676/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -30019,7 +30019,7 @@
           <t>C | 845呎 (2房)
 $2824万
 $33,422/呎
-(20年-05月-31日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -30027,7 +30027,7 @@
           <t>D | 939呎 (2房)
 $2644万
 $28,160/呎
-(20年-05月-19日)</t>
+(20年-05月)</t>
         </is>
       </c>
     </row>
@@ -30042,7 +30042,7 @@
           <t>A | 1118呎 (3房)
 $2395万
 $21,419/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -30050,7 +30050,7 @@
           <t>B | 1153呎 (3房)
 $2359万
 $20,460/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -30058,7 +30058,7 @@
           <t>C | 845呎 (2房)
 $1775万
 $21,001/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -30066,7 +30066,7 @@
           <t>D | 844呎 (2房)
 $1624万
 $19,247/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -30081,7 +30081,7 @@
           <t>A | 1118呎 (3房)
 $2368万
 $21,177/呎
-(25年-01月-05日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -30089,7 +30089,7 @@
           <t>B | 1153呎 (3房)
 $2297万
 $19,919/呎
-(25年-10月-16日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -30097,7 +30097,7 @@
           <t>C | 845呎 (2房)
 $1765万
 $20,891/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -30105,7 +30105,7 @@
           <t>D | 844呎 (2房)
 $1620万
 $19,192/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -30120,7 +30120,7 @@
           <t>A | 1118呎 (3房)
 $2364万
 $21,144/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -30128,7 +30128,7 @@
           <t>B | 1153呎 (3房)
 $2297万
 $19,919/呎
-(26年-01月-18日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -30136,7 +30136,7 @@
           <t>C | 845呎 (2房)
 $1763万
 $20,869/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -30144,7 +30144,7 @@
           <t>D | 844呎 (2房)
 $1619万
 $19,181/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -30159,7 +30159,7 @@
           <t>A | 1118呎 (3房)
 $2337万
 $20,902/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -30167,7 +30167,7 @@
           <t>B | 1153呎 (3房)
 $2290万
 $19,864/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -30175,7 +30175,7 @@
           <t>C | 845呎 (2房)
 $1756万
 $20,780/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -30183,7 +30183,7 @@
           <t>D | 844呎 (2房)
 $1619万
 $19,181/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -30198,7 +30198,7 @@
           <t>A | 1118呎 (3房)
 $2313万
 $20,691/呎
-(25年-10月-29日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -30206,7 +30206,7 @@
           <t>B | 1153呎 (3房)
 $2284万
 $19,810/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -30214,7 +30214,7 @@
           <t>C | 829呎 (2房)
 $1726万
 $20,818/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -30222,7 +30222,7 @@
           <t>D | 844呎 (2房)
 $1618万
 $19,169/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -30497,7 +30497,7 @@
           <t>C | 890呎 (2房)
 $2065万
 $23,200/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -30536,7 +30536,7 @@
           <t>C | 890呎 (2房)
 $2031万
 $22,820/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -30575,7 +30575,7 @@
           <t>C | 813呎 (2房)
 $2011万
 $24,740/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -30583,7 +30583,7 @@
           <t>D | 812呎 (2房)
 $1962万
 $24,167/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -30614,7 +30614,7 @@
           <t>C | 813呎 (2房)
 $2003万
 $24,637/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -30622,7 +30622,7 @@
           <t>D | 812呎 (2房)
 $1953万
 $24,058/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -30653,7 +30653,7 @@
           <t>C | 813呎 (2房)
 $1878万
 $23,098/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -30661,7 +30661,7 @@
           <t>D | 812呎 (2房)
 $1838万
 $22,630/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -30692,7 +30692,7 @@
           <t>C | 813呎 (2房)
 $1863万
 $22,912/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -30700,7 +30700,7 @@
           <t>D | 812呎 (2房)
 $1829万
 $22,520/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -30731,7 +30731,7 @@
           <t>C | 813呎 (2房)
 $1927万
 $23,700/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -30739,7 +30739,7 @@
           <t>D | 812呎 (2房)
 $1882万
 $23,177/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -30770,7 +30770,7 @@
           <t>C | 813呎 (2房)
 $1829万
 $22,496/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -30778,7 +30778,7 @@
           <t>D | 812呎 (2房)
 $1797万
 $22,135/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -30809,7 +30809,7 @@
           <t>C | 813呎 (2房)
 $1816万
 $22,332/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -30817,7 +30817,7 @@
           <t>D | 812呎 (2房)
 $1793万
 $22,080/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -30848,7 +30848,7 @@
           <t>C | 813呎 (2房)
 $1798万
 $22,113/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -30856,7 +30856,7 @@
           <t>D | 812呎 (2房)
 $1869万
 $23,014/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -30887,7 +30887,7 @@
           <t>C | 813呎 (2房)
 $1860万
 $22,879/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -30895,7 +30895,7 @@
           <t>D | 812呎 (2房)
 $1860万
 $22,904/呎
-(26年-06月-21日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -30926,7 +30926,7 @@
           <t>C | 890呎 (2房)
 $1865万
 $20,950/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -31113,7 +31113,7 @@
           <t>C | 1595呎 (4+房)
 $4779万
 $29,964/呎
-(25年-01月-27日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr"/>
@@ -31121,45 +31121,45 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1924万
+$23,811/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1934万
+$23,931/呎
+(24年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20&amp;21</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 2905呎 (4+房)
 $9870万
 $33,976/呎
-(26年-04月-12日)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1924万
-$23,811/呎
-(24年-03月-17日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1934万
-$23,931/呎
-(24年-02月-01日)</t>
-        </is>
-      </c>
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31172,7 +31172,7 @@
           <t>A | 2258呎 (4+房)
 $7128万
 $31,568/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
@@ -31191,7 +31191,7 @@
           <t>B | 1264呎 (3房)
 $3021万
 $23,902/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -31199,7 +31199,7 @@
           <t>C | 808呎 (2房)
 $1912万
 $23,663/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -31207,7 +31207,7 @@
           <t>D | 808呎 (2房)
 $1916万
 $23,712/呎
-(24年-01月-11日)</t>
+(24年-01月)</t>
         </is>
       </c>
     </row>
@@ -31222,7 +31222,7 @@
           <t>A | 1266呎 (3房)
 $3067万
 $24,230/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -31230,7 +31230,7 @@
           <t>B | 1264呎 (3房)
 $3043万
 $24,074/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -31238,7 +31238,7 @@
           <t>C | 808呎 (2房)
 $1883万
 $23,308/呎
-(23年-12月-11日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -31246,7 +31246,7 @@
           <t>D | 808呎 (2房)
 $1903万
 $23,547/呎
-(24年-01月-17日)</t>
+(24年-01月)</t>
         </is>
       </c>
     </row>
@@ -31261,7 +31261,7 @@
           <t>A | 1266呎 (3房)
 $2983万
 $23,562/呎
-(24年-03月-19日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -31269,7 +31269,7 @@
           <t>B | 1264呎 (3房)
 $2891万
 $22,873/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -31277,7 +31277,7 @@
           <t>C | 878呎 (2房)
 $1844万
 $21,000/呎
-(23年-11月-21日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -31285,7 +31285,7 @@
           <t>D | 887呎 (2房)
 $1836万
 $20,700/呎
-(23年-10月-16日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -31300,7 +31300,7 @@
           <t>A | 1266呎 (3房)
 $2805万
 $22,158/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -31308,7 +31308,7 @@
           <t>B | 1264呎 (3房)
 $2789万
 $22,065/呎
-(26年-01月-29日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -31316,7 +31316,7 @@
           <t>C | 878呎 (2房)
 $1809万
 $20,600/呎
-(23年-11月-12日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -31324,7 +31324,7 @@
           <t>D | 887呎 (2房)
 $1836万
 $20,700/呎
-(23年-11月-01日)</t>
+(23年-11月)</t>
         </is>
       </c>
     </row>
@@ -31339,7 +31339,7 @@
           <t>A | 1266呎 (3房)
 $2832万
 $22,366/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -31347,7 +31347,7 @@
           <t>B | 1264呎 (3房)
 $2815万
 $22,272/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -31355,7 +31355,7 @@
           <t>C | 878呎 (2房)
 $1789万
 $20,380/呎
-(23年-10月-26日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -31363,7 +31363,7 @@
           <t>D | 887呎 (2房)
 $1827万
 $20,600/呎
-(23年-10月-26日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -31378,7 +31378,7 @@
           <t>A | 1266呎 (3房)
 $2804万
 $22,147/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -31386,7 +31386,7 @@
           <t>B | 1264呎 (3房)
 $2815万
 $22,272/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -31394,7 +31394,7 @@
           <t>C | 878呎 (2房)
 $1778万
 $20,251/呎
-(23年-10月-24日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -31402,7 +31402,7 @@
           <t>D | 887呎 (2房)
 $1801万
 $20,308/呎
-(23年-11月-05日)</t>
+(23年-11月)</t>
         </is>
       </c>
     </row>
@@ -31417,7 +31417,7 @@
           <t>A | 1266呎 (3房)
 $2755万
 $21,763/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -31425,7 +31425,7 @@
           <t>B | 1264呎 (3房)
 $2726万
 $21,562/呎
-(26年-01月-29日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -31433,7 +31433,7 @@
           <t>C | 808呎 (2房)
 $1757万
 $21,741/呎
-(23年-10月-11日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -31441,7 +31441,7 @@
           <t>D | 808呎 (2房)
 $1775万
 $21,964/呎
-(23年-10月-11日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -31456,7 +31456,7 @@
           <t>A | 1266呎 (3房)
 $2720万
 $21,489/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -31464,7 +31464,7 @@
           <t>B | 1380呎 (3房)
 $2892万
 $20,960/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -31472,7 +31472,7 @@
           <t>C | 878呎 (2房)
 $1782万
 $20,296/呎
-(23年-11月-09日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -31480,7 +31480,7 @@
           <t>D | 808呎 (2房)
 $1756万
 $21,738/呎
-(23年-10月-19日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -31495,7 +31495,7 @@
           <t>A | 1266呎 (3房)
 $2885万
 $22,791/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -31503,7 +31503,7 @@
           <t>B | 1380呎 (3房)
 $2867万
 $20,774/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -31511,7 +31511,7 @@
           <t>C | 878呎 (2房)
 $1760万
 $20,050/呎
-(23年-10月-25日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -31519,7 +31519,7 @@
           <t>D | 887呎 (2房)
 $1747万
 $19,700/呎
-(23年-10月-26日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
           <t>A | 1266呎 (3房)
 $2679万
 $21,160/呎
-(25年-04月-10日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -31542,7 +31542,7 @@
           <t>B | 1264呎 (3房)
 $2663万
 $21,071/呎
-(25年-05月-08日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -31550,7 +31550,7 @@
           <t>C | 878呎 (2房)
 $1668万
 $19,000/呎
-(23年-10月-16日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -31558,7 +31558,7 @@
           <t>D | 808呎 (2房)
 $1774万
 $21,955/呎
-(23年-12月-07日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -31573,7 +31573,7 @@
           <t>A | 1388呎 (3房)
 $2720万
 $19,600/呎
-(23年-10月-18日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -31581,7 +31581,7 @@
           <t>B | 1380呎 (3房)
 $2705万
 $19,600/呎
-(23年-10月-29日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -31589,7 +31589,7 @@
           <t>C | 808呎 (2房)
 $1743万
 $21,570/呎
-(23年-12月-10日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -31597,7 +31597,7 @@
           <t>D | 808呎 (2房)
 $1761万
 $21,791/呎
-(23年-12月-06日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -31612,7 +31612,7 @@
           <t>A | 1388呎 (3房)
 $2769万
 $19,950/呎
-(23年-11月-26日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -31620,7 +31620,7 @@
           <t>B | 1264呎 (3房)
 $2839万
 $22,462/呎
-(23年-12月-03日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -31628,7 +31628,7 @@
           <t>C | 878呎 (2房)
 $1708万
 $19,450/呎
-(23年-12月-04日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -31636,7 +31636,7 @@
           <t>D | 887呎 (2房)
 $1730万
 $19,500/呎
-(23年-10月-30日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -31651,7 +31651,7 @@
           <t>A | 1388呎 (3房)
 $2693万
 $19,400/呎
-(23年-11月-14日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -31659,7 +31659,7 @@
           <t>B | 1264呎 (3房)
 $2677万
 $21,180/呎
-(23年-11月-14日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -31667,7 +31667,7 @@
           <t>C | 808呎 (2房)
 $1710万
 $21,168/呎
-(23年-12月-18日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -31675,7 +31675,7 @@
           <t>D | 808呎 (2房)
 $1762万
 $21,803/呎
-(23年-12月-03日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -31690,7 +31690,7 @@
           <t>A | 1266呎 (3房)
 $2741万
 $21,653/呎
-(23年-12月-18日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -31698,7 +31698,7 @@
           <t>B | 1264呎 (3房)
 $2732万
 $21,617/呎
-(24年-02月-07日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -31706,7 +31706,7 @@
           <t>C | 808呎 (2房)
 $1677万
 $20,755/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -31714,7 +31714,7 @@
           <t>D | 887呎 (2房)
 $1685万
 $19,000/呎
-(23年-10月-23日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -31729,7 +31729,7 @@
           <t>A | 1250呎 (3房)
 $2483万
 $19,866/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -31737,7 +31737,7 @@
           <t>B | 1264呎 (3房)
 $2484万
 $19,652/呎
-(25年-05月-19日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -31745,7 +31745,7 @@
           <t>C | 753呎 (2房)
 $1566万
 $20,797/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -31753,7 +31753,7 @@
           <t>D | 753呎 (2房)
 $1583万
 $21,019/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -31886,7 +31886,7 @@
           <t>B | 3236呎 (4+房)
 $11446万
 $35,371/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -31909,7 +31909,7 @@
           <t>A | 2271呎 (4+房)
 $7508万
 $33,060/呎
-(25年-11月-23日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr"/>
@@ -31927,7 +31927,7 @@
           <t>B | 1352呎 (3房)
 $3628万
 $26,833/呎
-(26年-01月-18日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -31935,7 +31935,7 @@
           <t>C | 785呎 (2房)
 $1849万
 $23,558/呎
-(24年-06月-16日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -31950,7 +31950,7 @@
           <t>A | 1321呎 (3房)
 $3526万
 $26,694/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -31958,7 +31958,7 @@
           <t>B | 1340呎 (3房)
 $3558万
 $26,551/呎
-(26年-01月-18日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -31966,7 +31966,7 @@
           <t>C | 785呎 (2房)
 $1833万
 $23,350/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -31981,7 +31981,7 @@
           <t>A | 1321呎 (3房)
 $3484万
 $26,376/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -31989,7 +31989,7 @@
           <t>B | 1340呎 (3房)
 $3139万
 $23,428/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -31997,7 +31997,7 @@
           <t>C | 785呎 (2房)
 $1798万
 $22,911/呎
-(24年-05月-06日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -32028,7 +32028,7 @@
           <t>C | 785呎 (2房)
 $1778万
 $22,644/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -32043,7 +32043,7 @@
           <t>A | 1321呎 (3房)
 $3115万
 $23,584/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -32051,7 +32051,7 @@
           <t>B | 1340呎 (3房)
 $3136万
 $23,400/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -32059,7 +32059,7 @@
           <t>C | 785呎 (2房)
 $1754万
 $22,340/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -32074,7 +32074,7 @@
           <t>A | 1321呎 (3房)
 $3110万
 $23,544/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -32090,7 +32090,7 @@
           <t>C | 785呎 (2房)
 $1618万
 $20,611/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -32105,7 +32105,7 @@
           <t>A | 1321呎 (3房)
 $3082万
 $23,332/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -32121,7 +32121,7 @@
           <t>C | 785呎 (2房)
 $1598万
 $20,357/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -32136,7 +32136,7 @@
           <t>A | 1321呎 (3房)
 $3050万
 $23,089/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -32152,7 +32152,7 @@
           <t>C | 785呎 (2房)
 $1569万
 $19,985/呎
-(25年-05月-21日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -32167,7 +32167,7 @@
           <t>A | 1321呎 (3房)
 $3030万
 $22,940/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -32175,7 +32175,7 @@
           <t>B | 1340呎 (3房)
 $3030万
 $22,612/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -32183,7 +32183,7 @@
           <t>C | 785呎 (2房)
 $1567万
 $19,963/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -32198,7 +32198,7 @@
           <t>A | 1401呎 (3房)
 $3512万
 $25,070/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -32206,7 +32206,7 @@
           <t>B | 1415呎 (3房)
 $3141万
 $22,200/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -32214,7 +32214,7 @@
           <t>C | 785呎 (2房)
 $1543万
 $19,661/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32229,7 @@
           <t>A | 1321呎 (3房)
 $2988万
 $22,621/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -32237,7 +32237,7 @@
           <t>B | 1340呎 (3房)
 $2990万
 $22,313/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -32245,7 +32245,7 @@
           <t>C | 785呎 (2房)
 $1539万
 $19,607/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -32260,7 +32260,7 @@
           <t>A | 1321呎 (3房)
 $3068万
 $23,226/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -32276,7 +32276,7 @@
           <t>C | 785呎 (2房)
 $1526万
 $19,445/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -32291,7 +32291,7 @@
           <t>A | 1321呎 (3房)
 $2921万
 $22,113/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -32307,7 +32307,7 @@
           <t>C | 785呎 (2房)
 $1522万
 $19,391/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -32322,7 +32322,7 @@
           <t>A | 1321呎 (3房)
 $2928万
 $22,166/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -32338,7 +32338,7 @@
           <t>C | 785呎 (2房)
 $1509万
 $19,229/呎
-(26年-01月-18日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -32369,7 +32369,7 @@
           <t>C | 785呎 (2房)
 $1503万
 $19,142/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-傲玟.xlsx
+++ b/files/九龙-何文田-傲玟.xlsx
@@ -4405,23 +4405,19 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>26896500</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>21500</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4430,12 +4426,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4445,7 +4441,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16605,23 +16601,19 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H241" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I241" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H241" s="5" t="n">
+        <v>20138000</v>
+      </c>
+      <c r="I241" s="5" t="n">
+        <v>22576</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
@@ -16630,12 +16622,12 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
@@ -16645,7 +16637,7 @@
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16881,23 +16873,19 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H245" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I245" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H245" s="5" t="n">
+        <v>19868000</v>
+      </c>
+      <c r="I245" s="5" t="n">
+        <v>22274</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
@@ -16906,12 +16894,12 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
@@ -16921,7 +16909,7 @@
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27576,7 +27564,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27586,7 +27574,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27635,18 +27623,35 @@
           <t>C | 2357呎 (4+房)
 $7787万
 $33,037/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 6681呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1442呎 (1房)
 -
@@ -27654,7 +27659,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27663,23 +27668,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 6681呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -27691,7 +27679,7 @@
           <t>A | 2669呎 (4+房)
 $7877万
 $29,514/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
@@ -27700,7 +27688,7 @@
           <t>C | 1186呎 (3房)
 $3125万
 $26,347/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27703,7 @@
           <t>A | 1367呎 (3房)
 $3612万
 $26,426/呎
-(24年-07月)</t>
+(24年-07月-25日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -27723,7 +27711,7 @@
           <t>B | 1368呎 (3房)
 $3618万
 $26,444/呎
-(24年-07月)</t>
+(24年-07月-25日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -27731,7 +27719,7 @@
           <t>C | 1186呎 (3房)
 $3002万
 $25,315/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -27746,7 +27734,7 @@
           <t>A | 1367呎 (3房)
 $3500万
 $25,604/呎
-(24年-10月)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -27754,7 +27742,7 @@
           <t>B | 1368呎 (3房)
 $3473万
 $25,386/呎
-(24年-12月)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -27777,7 +27765,7 @@
           <t>A | 1367呎 (3房)
 $3454万
 $25,264/呎
-(25年-03月)</t>
+(25年-03月-02日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -27785,7 +27773,7 @@
           <t>B | 1368呎 (3房)
 $3429万
 $25,069/呎
-(25年-03月)</t>
+(25年-03月-02日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -27808,7 +27796,7 @@
           <t>A | 1367呎 (3房)
 $3432万
 $25,105/呎
-(24年-12月)</t>
+(24年-12月-15日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -27816,7 +27804,7 @@
           <t>B | 1368呎 (3房)
 $3742万
 $27,350/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -27839,7 +27827,7 @@
           <t>A | 1367呎 (3房)
 $3425万
 $25,052/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -27847,7 +27835,7 @@
           <t>B | 1368呎 (3房)
 $3734万
 $27,297/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -27870,7 +27858,7 @@
           <t>A | 1367呎 (3房)
 $3417万
 $24,999/呎
-(24年-12月)</t>
+(24年-12月-15日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -27878,7 +27866,7 @@
           <t>B | 1368呎 (3房)
 $3727万
 $27,244/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
@@ -27901,7 +27889,7 @@
           <t>A | 1367呎 (3房)
 $3417万
 $24,999/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -27909,7 +27897,7 @@
           <t>B | 1368呎 (3房)
 $3340万
 $24,415/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -27917,7 +27905,7 @@
           <t>C | 1186呎 (3房)
 $2753万
 $23,210/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -27932,7 +27920,7 @@
           <t>A | 1367呎 (3房)
 $3396万
 $24,841/呎
-(24年-11月)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -27940,7 +27928,7 @@
           <t>B | 1368呎 (3房)
 $3321万
 $24,275/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -27948,7 +27936,7 @@
           <t>C | 1186呎 (3房)
 $2852万
 $24,050/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -27963,7 +27951,7 @@
           <t>A | 1367呎 (3房)
 $3403万
 $24,894/呎
-(24年-12月)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -27971,7 +27959,7 @@
           <t>B | 1368呎 (3房)
 $3313万
 $24,218/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -27979,7 +27967,7 @@
           <t>C | 1186呎 (3房)
 $2830万
 $23,860/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -27994,7 +27982,7 @@
           <t>A | 1367呎 (3房)
 $4198万
 $30,710/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -28002,7 +27990,7 @@
           <t>B | 1368呎 (3房)
 $3270万
 $23,905/呎
-(25年-08月)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
@@ -28025,7 +28013,7 @@
           <t>A | 1367呎 (3房)
 $3374万
 $24,682/呎
-(25年-01月)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -28033,7 +28021,7 @@
           <t>B | 1368呎 (3房)
 $3227万
 $23,588/呎
-(24年-08月)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -28041,7 +28029,7 @@
           <t>C | 1186呎 (3房)
 $2792万
 $23,543/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -28056,7 +28044,7 @@
           <t>A | 1367呎 (3房)
 $3665万
 $26,811/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -28064,7 +28052,7 @@
           <t>B | 1368呎 (3房)
 $3270万
 $23,905/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -28072,7 +28060,7 @@
           <t>C | 1251呎 (3房)
 $2815万
 $22,500/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -28087,7 +28075,7 @@
           <t>A | 1367呎 (3房)
 $3338万
 $24,418/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -28095,7 +28083,7 @@
           <t>B | 1368呎 (3房)
 $3205万
 $23,429/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -28118,7 +28106,7 @@
           <t>A | 1367呎 (3房)
 $3330万
 $24,360/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -28126,7 +28114,7 @@
           <t>B | 1368呎 (3房)
 $3212万
 $23,482/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
@@ -28149,7 +28137,7 @@
           <t>A | 1367呎 (3房)
 $3352万
 $24,524/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -28157,7 +28145,7 @@
           <t>B | 1368呎 (3房)
 $3209万
 $23,461/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
@@ -28180,7 +28168,7 @@
           <t>A | 1367呎 (3房)
 $3324万
 $24,312/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -28188,7 +28176,7 @@
           <t>B | 1368呎 (3房)
 $3193万
 $23,342/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -28211,7 +28199,7 @@
           <t>A | 1367呎 (3房)
 $3604万
 $26,364/呎
-(25年-02月)</t>
+(25年-02月-16日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -28219,15 +28207,15 @@
           <t>B | 1368呎 (3房)
 $3180万
 $23,246/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
+$2690万
+$21,500/呎
+(26年-07月-19日)</t>
         </is>
       </c>
     </row>
@@ -28242,7 +28230,7 @@
           <t>A | 1367呎 (3房)
 $3652万
 $26,719/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -28250,7 +28238,7 @@
           <t>B | 1368呎 (3房)
 $3154万
 $23,059/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -28258,7 +28246,7 @@
           <t>C | 1186呎 (3房)
 $2555万
 $21,539/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -28273,7 +28261,7 @@
           <t>A | 1445呎 (3房)
 $4494万
 $31,100/呎
-(20年-06月)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -28281,7 +28269,7 @@
           <t>B | 1368呎 (3房)
 $3133万
 $22,901/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -28289,7 +28277,7 @@
           <t>C | 1186呎 (3房)
 $2540万
 $21,413/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -28304,7 +28292,7 @@
           <t>A | 1367呎 (3房)
 $3100万
 $22,677/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -28312,7 +28300,7 @@
           <t>B | 1352呎 (3房)
 $3032万
 $22,423/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -28320,7 +28308,7 @@
           <t>C | 1186呎 (3房)
 $2527万
 $21,307/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28323,7 @@
           <t>A | 2626呎 (4+房)
 $6828万
 $26,000/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr"/>
@@ -28477,7 +28465,7 @@
           <t>B | 3461呎 (4+房)
 $12067万
 $34,864/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -28485,7 +28473,7 @@
           <t>C | 2334呎 (4+房)
 $7700万
 $32,991/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -28501,7 +28489,7 @@
           <t>B | 1351呎 (3房)
 $3630万
 $26,866/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -28509,7 +28497,7 @@
           <t>C | 1180呎 (3房)
 $2612万
 $22,139/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28512,7 @@
           <t>A | 2338呎 (4+房)
 $7600万
 $32,506/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -28541,7 +28529,7 @@
           <t>A | 1325呎 (3房)
 $3493万
 $26,366/呎
-(24年-01月)</t>
+(24年-01月-24日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -28549,7 +28537,7 @@
           <t>B | 1347呎 (3房)
 $3548万
 $26,342/呎
-(24年-01月)</t>
+(24年-01月-25日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -28557,7 +28545,7 @@
           <t>C | 1180呎 (3房)
 $2662万
 $22,561/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -28572,7 +28560,7 @@
           <t>A | 1325呎 (3房)
 $3479万
 $26,260/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -28580,7 +28568,7 @@
           <t>B | 1347呎 (3房)
 $3491万
 $25,919/呎
-(23年-10月)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -28588,7 +28576,7 @@
           <t>C | 1180呎 (3房)
 $2700万
 $22,881/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -28603,7 +28591,7 @@
           <t>A | 1403呎 (3房)
 $3115万
 $22,200/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -28611,7 +28599,7 @@
           <t>B | 1425呎 (3房)
 $3164万
 $22,200/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -28619,7 +28607,7 @@
           <t>C | 1180呎 (3房)
 $2612万
 $22,139/呎
-(24年-08月)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
     </row>
@@ -28634,7 +28622,7 @@
           <t>A | 1325呎 (3房)
 $3227万
 $24,354/呎
-(24年-02月)</t>
+(24年-02月-05日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -28642,7 +28630,7 @@
           <t>B | 1347呎 (3房)
 $3349万
 $24,861/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -28650,7 +28638,7 @@
           <t>C | 1180呎 (3房)
 $2995万
 $25,380/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -28665,7 +28653,7 @@
           <t>A | 1403呎 (3房)
 $3073万
 $21,900/呎
-(23年-10月)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -28673,7 +28661,7 @@
           <t>B | 1425呎 (3房)
 $3121万
 $21,900/呎
-(23年-10月)</t>
+(23年-10月-23日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -28681,7 +28669,7 @@
           <t>C | 1180呎 (3房)
 $2749万
 $23,299/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -28696,7 +28684,7 @@
           <t>A | 1403呎 (3房)
 $3087万
 $22,000/呎
-(23年-10月)</t>
+(23年-10月-30日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -28704,7 +28692,7 @@
           <t>B | 1347呎 (3房)
 $3206万
 $23,803/呎
-(23年-12月)</t>
+(23年-12月-11日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -28712,7 +28700,7 @@
           <t>C | 1180呎 (3房)
 $3084万
 $26,139/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -28727,7 +28715,7 @@
           <t>A | 1403呎 (3房)
 $3146万
 $22,420/呎
-(23年-11月)</t>
+(23年-11月-13日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -28735,7 +28723,7 @@
           <t>B | 1425呎 (3房)
 $3120万
 $21,896/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -28743,7 +28731,7 @@
           <t>C | 1180呎 (3房)
 $2608万
 $22,099/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -28758,7 +28746,7 @@
           <t>A | 1403呎 (3房)
 $3199万
 $22,800/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -28766,7 +28754,7 @@
           <t>B | 1347呎 (3房)
 $3164万
 $23,486/呎
-(24年-01月)</t>
+(24年-01月-02日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -28774,7 +28762,7 @@
           <t>C | 1180呎 (3房)
 $2692万
 $22,814/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -28789,7 +28777,7 @@
           <t>A | 1325呎 (3房)
 $3115万
 $23,507/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -28797,7 +28785,7 @@
           <t>B | 1347呎 (3房)
 $3164万
 $23,486/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -28805,7 +28793,7 @@
           <t>C | 1180呎 (3房)
 $2580万
 $21,864/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -28820,7 +28808,7 @@
           <t>A | 1403呎 (3房)
 $3016万
 $21,500/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -28828,7 +28816,7 @@
           <t>B | 1425呎 (3房)
 $2878万
 $20,200/呎
-(23年-10月)</t>
+(23年-10月-12日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -28836,7 +28824,7 @@
           <t>C | 1180呎 (3房)
 $2532万
 $21,454/呎
-(24年-03月)</t>
+(24年-03月-05日)</t>
         </is>
       </c>
     </row>
@@ -28851,7 +28839,7 @@
           <t>A | 1403呎 (3房)
 $4378万
 $31,206/呎
-(20年-05月)</t>
+(20年-05月-17日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -28859,7 +28847,7 @@
           <t>B | 1425呎 (3房)
 $2861万
 $20,080/呎
-(23年-10月)</t>
+(23年-10月-05日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -28867,7 +28855,7 @@
           <t>C | 1180呎 (3房)
 $2488万
 $21,085/呎
-(24年-01月)</t>
+(24年-01月-28日)</t>
         </is>
       </c>
     </row>
@@ -28882,7 +28870,7 @@
           <t>A | 1403呎 (3房)
 $2921万
 $20,820/呎
-(23年-11月)</t>
+(23年-11月-08日)</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
@@ -28898,7 +28886,7 @@
           <t>C | 1244呎 (3房)
 $2513万
 $20,200/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -28913,7 +28901,7 @@
           <t>A | 1325呎 (3房)
 $2908万
 $21,947/呎
-(23年-12月)</t>
+(23年-12月-06日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -28921,7 +28909,7 @@
           <t>B | 1425呎 (3房)
 $2850万
 $20,000/呎
-(23年-10月)</t>
+(23年-10月-30日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -28929,7 +28917,7 @@
           <t>C | 1180呎 (3房)
 $2415万
 $20,464/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -28944,7 +28932,7 @@
           <t>A | 1325呎 (3房)
 $2868万
 $21,642/呎
-(23年-12月)</t>
+(23年-12月-05日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -28952,7 +28940,7 @@
           <t>B | 1425呎 (3房)
 $4225万
 $29,650/呎
-(20年-05月)</t>
+(20年-05月-27日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -28960,7 +28948,7 @@
           <t>C | 1180呎 (3房)
 $2427万
 $20,570/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28963,7 @@
           <t>A | 1325呎 (3房)
 $2778万
 $20,966/呎
-(23年-10月)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -28983,7 +28971,7 @@
           <t>B | 1347呎 (3房)
 $4185万
 $31,066/呎
-(20年-05月)</t>
+(20年-05月-17日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -28991,7 +28979,7 @@
           <t>C | 1180呎 (3房)
 $2140万
 $18,133/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
     </row>
@@ -29006,7 +28994,7 @@
           <t>A | 1403呎 (3房)
 $4349万
 $31,000/呎
-(19年-12月)</t>
+(19年-12月-11日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -29014,7 +29002,7 @@
           <t>B | 1425呎 (3房)
 $4175万
 $29,295/呎
-(20年-05月)</t>
+(20年-05月-14日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -29022,7 +29010,7 @@
           <t>C | 1180呎 (3房)
 $2140万
 $18,133/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -29037,7 +29025,7 @@
           <t>A | 1403呎 (3房)
 $4021万
 $28,659/呎
-(20年-05月)</t>
+(20年-05月-25日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -29045,7 +29033,7 @@
           <t>B | 1425呎 (3房)
 $4118万
 $28,902/呎
-(20年-05月)</t>
+(20年-05月-14日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -29053,7 +29041,7 @@
           <t>C | 1180呎 (3房)
 $2132万
 $18,070/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
     </row>
@@ -29068,7 +29056,7 @@
           <t>A | 1325呎 (3房)
 $3934万
 $29,690/呎
-(20年-05月)</t>
+(20年-05月-17日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -29076,7 +29064,7 @@
           <t>B | 1347呎 (3房)
 $4086万
 $30,332/呎
-(20年-05月)</t>
+(20年-05月-17日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -29084,7 +29072,7 @@
           <t>C | 1180呎 (3房)
 $2131万
 $18,059/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
     </row>
@@ -29099,7 +29087,7 @@
           <t>A | 1403呎 (3房)
 $3931万
 $28,018/呎
-(20年-05月)</t>
+(20年-05月-19日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -29107,7 +29095,7 @@
           <t>B | 1425呎 (3房)
 $4053万
 $28,445/呎
-(20年-05月)</t>
+(20年-05月-27日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -29115,7 +29103,7 @@
           <t>C | 1180呎 (3房)
 $2130万
 $18,049/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -29130,7 +29118,7 @@
           <t>A | 1403呎 (3房)
 $3931万
 $28,018/呎
-(21年-03月)</t>
+(21年-03月-30日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -29138,7 +29126,7 @@
           <t>B | 1425呎 (3房)
 $4041万
 $28,360/呎
-(20年-12月)</t>
+(20年-12月-23日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -29146,7 +29134,7 @@
           <t>C | 1180呎 (3房)
 $2128万
 $18,038/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -29161,7 +29149,7 @@
           <t>A | 1325呎 (3房)
 $2804万
 $21,163/呎
-(24年-01月)</t>
+(24年-01月-16日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -29169,7 +29157,7 @@
           <t>B | 1330呎 (3房)
 $2800万
 $21,053/呎
-(24年-01月)</t>
+(24年-01月-18日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -29177,7 +29165,7 @@
           <t>C | 1180呎 (3房)
 $2127万
 $18,027/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -29194,7 +29182,7 @@
           <t>C | 2251呎 (4+房)
 $5853万
 $26,000/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -29334,7 +29322,7 @@
           <t>C | 1683呎 (4+房)
 $5471万
 $32,505/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr"/>
@@ -29342,45 +29330,45 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
 $33,915/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
+(25年-02月-25日)</t>
+        </is>
+      </c>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29393,7 +29381,7 @@
           <t>A | 2065呎 (4+房)
 $6250万
 $30,266/呎
-(24年-02月)</t>
+(24年-02月-01日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
@@ -29402,7 +29390,7 @@
           <t>C | 845呎 (2房)
 $1978万
 $23,411/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -29410,7 +29398,7 @@
           <t>D | 845呎 (2房)
 $1883万
 $22,280/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -29425,7 +29413,7 @@
           <t>A | 2002呎 (4+房)
 $6254万
 $31,239/呎
-(24年-03月)</t>
+(24年-03月-04日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -29434,7 +29422,7 @@
           <t>C | 845呎 (2房)
 $1957万
 $23,157/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -29442,7 +29430,7 @@
           <t>D | 845呎 (2房)
 $1861万
 $22,025/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -29457,7 +29445,7 @@
           <t>A | 1118呎 (3房)
 $2677万
 $23,945/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -29465,7 +29453,7 @@
           <t>B | 1153呎 (3房)
 $2616万
 $22,689/呎
-(24年-10月)</t>
+(24年-10月-14日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -29473,7 +29461,7 @@
           <t>C | 845呎 (2房)
 $1915万
 $22,659/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -29481,7 +29469,7 @@
           <t>D | 844呎 (2房)
 $1840万
 $21,806/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -29496,7 +29484,7 @@
           <t>A | 1118呎 (3房)
 $2650万
 $23,703/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -29504,7 +29492,7 @@
           <t>B | 1153呎 (3房)
 $2579万
 $22,368/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -29512,7 +29500,7 @@
           <t>C | 845呎 (2房)
 $1943万
 $22,991/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -29520,7 +29508,7 @@
           <t>D | 844呎 (2房)
 $1822万
 $21,584/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -29535,7 +29523,7 @@
           <t>A | 1118呎 (3房)
 $2610万
 $23,345/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -29543,7 +29531,7 @@
           <t>B | 1153呎 (3房)
 $2558万
 $22,183/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -29551,7 +29539,7 @@
           <t>C | 845呎 (2房)
 $1868万
 $22,107/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -29559,7 +29547,7 @@
           <t>D | 844呎 (2房)
 $1803万
 $21,361/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29562,7 @@
           <t>A | 1118呎 (3房)
 $2892万
 $25,867/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -29582,7 +29570,7 @@
           <t>B | 1153呎 (3房)
 $2535万
 $21,987/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -29590,7 +29578,7 @@
           <t>C | 845呎 (2房)
 $1840万
 $21,775/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -29598,7 +29586,7 @@
           <t>D | 844呎 (2房)
 $1784万
 $21,139/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -29613,7 +29601,7 @@
           <t>A | 1118呎 (3房)
 $2560万
 $22,898/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -29621,7 +29609,7 @@
           <t>B | 1153呎 (3房)
 $2535万
 $21,987/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -29629,7 +29617,7 @@
           <t>C | 845呎 (2房)
 $1905万
 $22,549/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -29637,7 +29625,7 @@
           <t>D | 844呎 (2房)
 $1765万
 $20,916/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -29652,7 +29640,7 @@
           <t>A | 1118呎 (3房)
 $2542万
 $22,737/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -29660,7 +29648,7 @@
           <t>B | 1153呎 (3房)
 $2870万
 $24,892/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -29668,7 +29656,7 @@
           <t>C | 845呎 (2房)
 $1882万
 $22,272/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -29676,7 +29664,7 @@
           <t>D | 844呎 (2房)
 $1728万
 $20,471/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -29691,7 +29679,7 @@
           <t>A | 1118呎 (3房)
 $2535万
 $22,674/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -29699,7 +29687,7 @@
           <t>B | 1153呎 (3房)
 $2497万
 $21,660/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -29707,7 +29695,7 @@
           <t>C | 845呎 (2房)
 $1873万
 $22,162/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -29715,7 +29703,7 @@
           <t>D | 844呎 (2房)
 $1765万
 $20,916/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -29730,7 +29718,7 @@
           <t>A | 1118呎 (3房)
 $2505万
 $22,407/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -29738,7 +29726,7 @@
           <t>B | 1153呎 (3房)
 $2491万
 $21,606/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -29746,7 +29734,7 @@
           <t>C | 845呎 (2房)
 $1857万
 $21,974/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -29754,7 +29742,7 @@
           <t>D | 844呎 (2房)
 $1708万
 $20,237/呎
-(24年-12月)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -29769,7 +29757,7 @@
           <t>A | 1118呎 (3房)
 $2493万
 $22,297/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -29777,7 +29765,7 @@
           <t>B | 1153呎 (3房)
 $2465万
 $21,379/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -29785,7 +29773,7 @@
           <t>C | 845呎 (2房)
 $1840万
 $21,775/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -29793,7 +29781,7 @@
           <t>D | 844呎 (2房)
 $1694万
 $20,071/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
     </row>
@@ -29808,7 +29796,7 @@
           <t>A | 1118呎 (3房)
 $2473万
 $22,122/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -29816,7 +29804,7 @@
           <t>B | 1153呎 (3房)
 $2450万
 $21,249/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -29824,7 +29812,7 @@
           <t>C | 845呎 (2房)
 $1831万
 $21,664/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -29832,7 +29820,7 @@
           <t>D | 844呎 (2房)
 $1690万
 $20,026/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29835,7 @@
           <t>A | 1118呎 (3房)
 $2456万
 $21,968/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -29855,7 +29843,7 @@
           <t>B | 1153呎 (3房)
 $2426万
 $21,040/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -29863,7 +29851,7 @@
           <t>C | 845呎 (2房)
 $1812万
 $21,443/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -29871,7 +29859,7 @@
           <t>D | 844呎 (2房)
 $1662万
 $19,692/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -29886,7 +29874,7 @@
           <t>A | 1228呎 (3房)
 $3616万
 $29,450/呎
-(20年-07月)</t>
+(20年-07月-27日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -29894,7 +29882,7 @@
           <t>B | 1153呎 (3房)
 $2428万
 $21,062/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -29902,7 +29890,7 @@
           <t>C | 845呎 (2房)
 $1804万
 $21,344/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -29910,7 +29898,7 @@
           <t>D | 844呎 (2房)
 $1657万
 $19,637/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -29925,7 +29913,7 @@
           <t>A | 1118呎 (3房)
 $2438万
 $21,803/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -29933,7 +29921,7 @@
           <t>B | 1153呎 (3房)
 $2428万
 $21,062/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -29941,7 +29929,7 @@
           <t>C | 845呎 (2房)
 $1800万
 $21,302/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -29949,7 +29937,7 @@
           <t>D | 844呎 (2房)
 $1653万
 $19,581/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -29964,7 +29952,7 @@
           <t>A | 1118呎 (3房)
 $2419万
 $21,638/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -29972,7 +29960,7 @@
           <t>B | 1153呎 (3房)
 $2397万
 $20,789/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -29980,7 +29968,7 @@
           <t>C | 934呎 (2房)
 $2852万
 $30,538/呎
-(20年-07月)</t>
+(20年-07月-21日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -29988,7 +29976,7 @@
           <t>D | 844呎 (2房)
 $1648万
 $19,525/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -30003,7 +29991,7 @@
           <t>A | 1228呎 (3房)
 $3513万
 $28,610/呎
-(20年-06月)</t>
+(20年-06月-11日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -30011,7 +29999,7 @@
           <t>B | 1153呎 (3房)
 $2384万
 $20,676/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -30019,7 +30007,7 @@
           <t>C | 845呎 (2房)
 $2824万
 $33,422/呎
-(20年-05月)</t>
+(20年-05月-31日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -30027,7 +30015,7 @@
           <t>D | 939呎 (2房)
 $2644万
 $28,160/呎
-(20年-05月)</t>
+(20年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -30042,7 +30030,7 @@
           <t>A | 1118呎 (3房)
 $2395万
 $21,419/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -30050,7 +30038,7 @@
           <t>B | 1153呎 (3房)
 $2359万
 $20,460/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -30058,7 +30046,7 @@
           <t>C | 845呎 (2房)
 $1775万
 $21,001/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -30066,7 +30054,7 @@
           <t>D | 844呎 (2房)
 $1624万
 $19,247/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -30081,7 +30069,7 @@
           <t>A | 1118呎 (3房)
 $2368万
 $21,177/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -30089,7 +30077,7 @@
           <t>B | 1153呎 (3房)
 $2297万
 $19,919/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -30097,7 +30085,7 @@
           <t>C | 845呎 (2房)
 $1765万
 $20,891/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -30105,7 +30093,7 @@
           <t>D | 844呎 (2房)
 $1620万
 $19,192/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -30120,7 +30108,7 @@
           <t>A | 1118呎 (3房)
 $2364万
 $21,144/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -30128,7 +30116,7 @@
           <t>B | 1153呎 (3房)
 $2297万
 $19,919/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -30136,7 +30124,7 @@
           <t>C | 845呎 (2房)
 $1763万
 $20,869/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -30144,7 +30132,7 @@
           <t>D | 844呎 (2房)
 $1619万
 $19,181/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -30159,7 +30147,7 @@
           <t>A | 1118呎 (3房)
 $2337万
 $20,902/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -30167,7 +30155,7 @@
           <t>B | 1153呎 (3房)
 $2290万
 $19,864/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -30175,7 +30163,7 @@
           <t>C | 845呎 (2房)
 $1756万
 $20,780/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -30183,7 +30171,7 @@
           <t>D | 844呎 (2房)
 $1619万
 $19,181/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -30198,7 +30186,7 @@
           <t>A | 1118呎 (3房)
 $2313万
 $20,691/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -30206,7 +30194,7 @@
           <t>B | 1153呎 (3房)
 $2284万
 $19,810/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -30214,7 +30202,7 @@
           <t>C | 829呎 (2房)
 $1726万
 $20,818/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -30222,7 +30210,7 @@
           <t>D | 844呎 (2房)
 $1618万
 $19,169/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -30298,7 +30286,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30308,7 +30296,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30384,10 +30372,42 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 898呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 2403呎 (4+房)
 -
@@ -30395,26 +30415,33 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1399呎 (3房)
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
 -
@@ -30422,22 +30449,22 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>D | 898呎 (2房)
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 892呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30445,7 +30472,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30453,30 +30480,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
+$2065万
+$23,200/呎
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
+$2014万
+$22,576/呎
+(26年-07月-19日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30484,7 +30511,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30492,30 +30519,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
-$2065万
-$23,200/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
+$2031万
+$22,820/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
+$1987万
+$22,274/呎
+(26年-07月-19日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30523,7 +30550,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30531,30 +30558,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
-$2031万
-$22,820/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>D | 892呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2011万
+$24,740/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1962万
+$24,167/呎
+(26年-07月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30562,7 +30589,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30570,30 +30597,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$2011万
-$24,740/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
+$2003万
+$24,637/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1962万
-$24,167/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
+$1953万
+$24,058/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30601,7 +30628,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30609,30 +30636,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$2003万
-$24,637/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+$1878万
+$23,098/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1953万
-$24,058/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
+$1838万
+$22,630/呎
+(26年-06月-07日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30640,7 +30667,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30648,30 +30675,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1878万
-$23,098/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+$1863万
+$22,912/呎
+(26年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1838万
-$22,630/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
+$1829万
+$22,520/呎
+(26年-06月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30679,7 +30706,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30687,30 +30714,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1863万
-$22,912/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
+$1927万
+$23,700/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1829万
-$22,520/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
+$1882万
+$23,177/呎
+(26年-07月-01日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30718,7 +30745,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30726,30 +30753,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1927万
-$23,700/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+$1829万
+$22,496/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1882万
-$23,177/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
+$1797万
+$22,135/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30757,7 +30784,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30765,30 +30792,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1829万
-$22,496/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+$1816万
+$22,332/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1797万
-$22,135/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
+$1793万
+$22,080/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30796,7 +30823,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30804,30 +30831,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1816万
-$22,332/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
+$1798万
+$22,113/呎
+(26年-06月-07日)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1793万
-$22,080/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
+$1869万
+$23,014/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30835,7 +30862,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30843,30 +30870,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1798万
-$22,113/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
+$1860万
+$22,879/呎
+(26年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1869万
-$23,014/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
+$1860万
+$22,904/呎
+(26年-07月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30874,7 +30901,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30882,51 +30909,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1860万
-$22,879/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1860万
-$22,904/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
 $1865万
 $20,950/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -31113,7 +31101,7 @@
           <t>C | 1595呎 (4+房)
 $4779万
 $29,964/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr"/>
@@ -31131,7 +31119,7 @@
           <t>C | 808呎 (2房)
 $1924万
 $23,811/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -31139,7 +31127,7 @@
           <t>D | 808呎 (2房)
 $1934万
 $23,931/呎
-(24年-02月)</t>
+(24年-02月-01日)</t>
         </is>
       </c>
     </row>
@@ -31155,7 +31143,7 @@
           <t>B | 2905呎 (4+房)
 $9870万
 $33,976/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -31172,7 +31160,7 @@
           <t>A | 2258呎 (4+房)
 $7128万
 $31,568/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
@@ -31191,7 +31179,7 @@
           <t>B | 1264呎 (3房)
 $3021万
 $23,902/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -31199,7 +31187,7 @@
           <t>C | 808呎 (2房)
 $1912万
 $23,663/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -31207,7 +31195,7 @@
           <t>D | 808呎 (2房)
 $1916万
 $23,712/呎
-(24年-01月)</t>
+(24年-01月-11日)</t>
         </is>
       </c>
     </row>
@@ -31222,7 +31210,7 @@
           <t>A | 1266呎 (3房)
 $3067万
 $24,230/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -31230,7 +31218,7 @@
           <t>B | 1264呎 (3房)
 $3043万
 $24,074/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -31238,7 +31226,7 @@
           <t>C | 808呎 (2房)
 $1883万
 $23,308/呎
-(23年-12月)</t>
+(23年-12月-11日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -31246,7 +31234,7 @@
           <t>D | 808呎 (2房)
 $1903万
 $23,547/呎
-(24年-01月)</t>
+(24年-01月-17日)</t>
         </is>
       </c>
     </row>
@@ -31261,7 +31249,7 @@
           <t>A | 1266呎 (3房)
 $2983万
 $23,562/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -31269,7 +31257,7 @@
           <t>B | 1264呎 (3房)
 $2891万
 $22,873/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -31277,7 +31265,7 @@
           <t>C | 878呎 (2房)
 $1844万
 $21,000/呎
-(23年-11月)</t>
+(23年-11月-21日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -31285,7 +31273,7 @@
           <t>D | 887呎 (2房)
 $1836万
 $20,700/呎
-(23年-10月)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -31300,7 +31288,7 @@
           <t>A | 1266呎 (3房)
 $2805万
 $22,158/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -31308,7 +31296,7 @@
           <t>B | 1264呎 (3房)
 $2789万
 $22,065/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -31316,7 +31304,7 @@
           <t>C | 878呎 (2房)
 $1809万
 $20,600/呎
-(23年-11月)</t>
+(23年-11月-12日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -31324,7 +31312,7 @@
           <t>D | 887呎 (2房)
 $1836万
 $20,700/呎
-(23年-11月)</t>
+(23年-11月-01日)</t>
         </is>
       </c>
     </row>
@@ -31339,7 +31327,7 @@
           <t>A | 1266呎 (3房)
 $2832万
 $22,366/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -31347,7 +31335,7 @@
           <t>B | 1264呎 (3房)
 $2815万
 $22,272/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -31355,7 +31343,7 @@
           <t>C | 878呎 (2房)
 $1789万
 $20,380/呎
-(23年-10月)</t>
+(23年-10月-26日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -31363,7 +31351,7 @@
           <t>D | 887呎 (2房)
 $1827万
 $20,600/呎
-(23年-10月)</t>
+(23年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -31378,7 +31366,7 @@
           <t>A | 1266呎 (3房)
 $2804万
 $22,147/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -31386,7 +31374,7 @@
           <t>B | 1264呎 (3房)
 $2815万
 $22,272/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -31394,7 +31382,7 @@
           <t>C | 878呎 (2房)
 $1778万
 $20,251/呎
-(23年-10月)</t>
+(23年-10月-24日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -31402,7 +31390,7 @@
           <t>D | 887呎 (2房)
 $1801万
 $20,308/呎
-(23年-11月)</t>
+(23年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -31417,7 +31405,7 @@
           <t>A | 1266呎 (3房)
 $2755万
 $21,763/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -31425,7 +31413,7 @@
           <t>B | 1264呎 (3房)
 $2726万
 $21,562/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -31433,7 +31421,7 @@
           <t>C | 808呎 (2房)
 $1757万
 $21,741/呎
-(23年-10月)</t>
+(23年-10月-11日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -31441,7 +31429,7 @@
           <t>D | 808呎 (2房)
 $1775万
 $21,964/呎
-(23年-10月)</t>
+(23年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -31456,7 +31444,7 @@
           <t>A | 1266呎 (3房)
 $2720万
 $21,489/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -31464,7 +31452,7 @@
           <t>B | 1380呎 (3房)
 $2892万
 $20,960/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -31472,7 +31460,7 @@
           <t>C | 878呎 (2房)
 $1782万
 $20,296/呎
-(23年-11月)</t>
+(23年-11月-09日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -31480,7 +31468,7 @@
           <t>D | 808呎 (2房)
 $1756万
 $21,738/呎
-(23年-10月)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
     </row>
@@ -31495,7 +31483,7 @@
           <t>A | 1266呎 (3房)
 $2885万
 $22,791/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -31503,7 +31491,7 @@
           <t>B | 1380呎 (3房)
 $2867万
 $20,774/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -31511,7 +31499,7 @@
           <t>C | 878呎 (2房)
 $1760万
 $20,050/呎
-(23年-10月)</t>
+(23年-10月-25日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -31519,7 +31507,7 @@
           <t>D | 887呎 (2房)
 $1747万
 $19,700/呎
-(23年-10月)</t>
+(23年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31522,7 @@
           <t>A | 1266呎 (3房)
 $2679万
 $21,160/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -31542,7 +31530,7 @@
           <t>B | 1264呎 (3房)
 $2663万
 $21,071/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -31550,7 +31538,7 @@
           <t>C | 878呎 (2房)
 $1668万
 $19,000/呎
-(23年-10月)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -31558,7 +31546,7 @@
           <t>D | 808呎 (2房)
 $1774万
 $21,955/呎
-(23年-12月)</t>
+(23年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -31573,7 +31561,7 @@
           <t>A | 1388呎 (3房)
 $2720万
 $19,600/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -31581,7 +31569,7 @@
           <t>B | 1380呎 (3房)
 $2705万
 $19,600/呎
-(23年-10月)</t>
+(23年-10月-29日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -31589,7 +31577,7 @@
           <t>C | 808呎 (2房)
 $1743万
 $21,570/呎
-(23年-12月)</t>
+(23年-12月-10日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -31597,7 +31585,7 @@
           <t>D | 808呎 (2房)
 $1761万
 $21,791/呎
-(23年-12月)</t>
+(23年-12月-06日)</t>
         </is>
       </c>
     </row>
@@ -31612,7 +31600,7 @@
           <t>A | 1388呎 (3房)
 $2769万
 $19,950/呎
-(23年-11月)</t>
+(23年-11月-26日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -31620,7 +31608,7 @@
           <t>B | 1264呎 (3房)
 $2839万
 $22,462/呎
-(23年-12月)</t>
+(23年-12月-03日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -31628,7 +31616,7 @@
           <t>C | 878呎 (2房)
 $1708万
 $19,450/呎
-(23年-12月)</t>
+(23年-12月-04日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -31636,7 +31624,7 @@
           <t>D | 887呎 (2房)
 $1730万
 $19,500/呎
-(23年-10月)</t>
+(23年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -31651,7 +31639,7 @@
           <t>A | 1388呎 (3房)
 $2693万
 $19,400/呎
-(23年-11月)</t>
+(23年-11月-14日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -31659,7 +31647,7 @@
           <t>B | 1264呎 (3房)
 $2677万
 $21,180/呎
-(23年-11月)</t>
+(23年-11月-14日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -31667,7 +31655,7 @@
           <t>C | 808呎 (2房)
 $1710万
 $21,168/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -31675,7 +31663,7 @@
           <t>D | 808呎 (2房)
 $1762万
 $21,803/呎
-(23年-12月)</t>
+(23年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -31690,7 +31678,7 @@
           <t>A | 1266呎 (3房)
 $2741万
 $21,653/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -31698,7 +31686,7 @@
           <t>B | 1264呎 (3房)
 $2732万
 $21,617/呎
-(24年-02月)</t>
+(24年-02月-07日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -31706,7 +31694,7 @@
           <t>C | 808呎 (2房)
 $1677万
 $20,755/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -31714,7 +31702,7 @@
           <t>D | 887呎 (2房)
 $1685万
 $19,000/呎
-(23年-10月)</t>
+(23年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -31729,7 +31717,7 @@
           <t>A | 1250呎 (3房)
 $2483万
 $19,866/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -31737,7 +31725,7 @@
           <t>B | 1264呎 (3房)
 $2484万
 $19,652/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -31745,7 +31733,7 @@
           <t>C | 753呎 (2房)
 $1566万
 $20,797/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -31753,7 +31741,7 @@
           <t>D | 753呎 (2房)
 $1583万
 $21,019/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -31886,7 +31874,7 @@
           <t>B | 3236呎 (4+房)
 $11446万
 $35,371/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -31901,43 +31889,43 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1352呎 (3房)
+$3628万
+$26,833/呎
+(26年-01月-18日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1849万
+$23,558/呎
+(24年-06月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2271呎 (4+房)
 $7508万
 $33,060/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1352呎 (3房)
-$3628万
-$26,833/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1849万
-$23,558/呎
-(24年-06月)</t>
-        </is>
-      </c>
+(25年-11月-23日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31950,7 +31938,7 @@
           <t>A | 1321呎 (3房)
 $3526万
 $26,694/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -31958,7 +31946,7 @@
           <t>B | 1340呎 (3房)
 $3558万
 $26,551/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -31966,7 +31954,7 @@
           <t>C | 785呎 (2房)
 $1833万
 $23,350/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -31981,7 +31969,7 @@
           <t>A | 1321呎 (3房)
 $3484万
 $26,376/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -31989,7 +31977,7 @@
           <t>B | 1340呎 (3房)
 $3139万
 $23,428/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -31997,7 +31985,7 @@
           <t>C | 785呎 (2房)
 $1798万
 $22,911/呎
-(24年-05月)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -32028,7 +32016,7 @@
           <t>C | 785呎 (2房)
 $1778万
 $22,644/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -32043,7 +32031,7 @@
           <t>A | 1321呎 (3房)
 $3115万
 $23,584/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -32051,7 +32039,7 @@
           <t>B | 1340呎 (3房)
 $3136万
 $23,400/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -32059,7 +32047,7 @@
           <t>C | 785呎 (2房)
 $1754万
 $22,340/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -32074,7 +32062,7 @@
           <t>A | 1321呎 (3房)
 $3110万
 $23,544/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -32090,7 +32078,7 @@
           <t>C | 785呎 (2房)
 $1618万
 $20,611/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
     </row>
@@ -32105,7 +32093,7 @@
           <t>A | 1321呎 (3房)
 $3082万
 $23,332/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -32121,7 +32109,7 @@
           <t>C | 785呎 (2房)
 $1598万
 $20,357/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -32136,7 +32124,7 @@
           <t>A | 1321呎 (3房)
 $3050万
 $23,089/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -32152,7 +32140,7 @@
           <t>C | 785呎 (2房)
 $1569万
 $19,985/呎
-(25年-05月)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -32167,7 +32155,7 @@
           <t>A | 1321呎 (3房)
 $3030万
 $22,940/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -32175,7 +32163,7 @@
           <t>B | 1340呎 (3房)
 $3030万
 $22,612/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -32183,7 +32171,7 @@
           <t>C | 785呎 (2房)
 $1567万
 $19,963/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -32198,7 +32186,7 @@
           <t>A | 1401呎 (3房)
 $3512万
 $25,070/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -32206,7 +32194,7 @@
           <t>B | 1415呎 (3房)
 $3141万
 $22,200/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -32214,7 +32202,7 @@
           <t>C | 785呎 (2房)
 $1543万
 $19,661/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32217,7 @@
           <t>A | 1321呎 (3房)
 $2988万
 $22,621/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -32237,7 +32225,7 @@
           <t>B | 1340呎 (3房)
 $2990万
 $22,313/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -32245,7 +32233,7 @@
           <t>C | 785呎 (2房)
 $1539万
 $19,607/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -32260,7 +32248,7 @@
           <t>A | 1321呎 (3房)
 $3068万
 $23,226/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -32276,7 +32264,7 @@
           <t>C | 785呎 (2房)
 $1526万
 $19,445/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -32291,7 +32279,7 @@
           <t>A | 1321呎 (3房)
 $2921万
 $22,113/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -32307,7 +32295,7 @@
           <t>C | 785呎 (2房)
 $1522万
 $19,391/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
     </row>
@@ -32322,7 +32310,7 @@
           <t>A | 1321呎 (3房)
 $2928万
 $22,166/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -32338,7 +32326,7 @@
           <t>C | 785呎 (2房)
 $1509万
 $19,229/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
     </row>
@@ -32369,7 +32357,7 @@
           <t>C | 785呎 (2房)
 $1503万
 $19,142/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-傲玟.xlsx
+++ b/files/九龙-何文田-傲玟.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,11 +131,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -223,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -291,13 +286,10 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1799,7 +1791,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -16663,7 +16655,7 @@
         </is>
       </c>
       <c r="E242" s="4" t="n">
-        <v>890</v>
+        <v>813</v>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
@@ -16679,7 +16671,7 @@
         <v>20648000</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>23200</v>
+        <v>25397</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
@@ -27564,12 +27556,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -27812,7 +27804,7 @@
           <t>C | 1251呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -27869,7 +27861,7 @@
 (25年-04月-22日)</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -27993,7 +27985,7 @@
 (25年-08月-06日)</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -28117,7 +28109,7 @@
 (26年-03月-29日)</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -28148,7 +28140,7 @@
 (26年-04月-12日)</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -28873,7 +28865,7 @@
 (23年-11月-08日)</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>B | 1347呎 (3房)
 -
@@ -30372,11 +30364,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1399呎 (3房)
 -
@@ -30384,7 +30394,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
 -
@@ -30392,7 +30402,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 898呎 (2房)
 -
@@ -30401,24 +30411,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -30482,9 +30474,9 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>C | 890呎 (2房)
+          <t>C | 813呎 (2房)
 $2065万
-$23,200/呎
+$25,397/呎
 (26年-07月-05日)</t>
         </is>
       </c>
@@ -31889,11 +31881,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2271呎 (4+房)
+$7508万
+$33,060/呎
+(25年-11月-23日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1352呎 (3房)
 $3628万
@@ -31901,7 +31910,7 @@
 (26年-01月-18日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 785呎 (2房)
 $1849万
@@ -31910,23 +31919,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2271呎 (4+房)
-$7508万
-$33,060/呎
-(25年-11月-23日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -32065,7 +32057,7 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
@@ -32096,7 +32088,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
@@ -32127,7 +32119,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
@@ -32251,7 +32243,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
@@ -32282,7 +32274,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
@@ -32313,7 +32305,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
